--- a/artfynd/A 8191-2026 artfynd.xlsx
+++ b/artfynd/A 8191-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ116"/>
+  <dimension ref="A1:AZ122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4768,27 +4768,27 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125805740</v>
+        <v>136969495</v>
       </c>
       <c r="B39" t="n">
-        <v>57953</v>
+        <v>58005</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4807,17 +4807,17 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>HACKMORA, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>512523</v>
+        <v>512442</v>
       </c>
       <c r="R39" t="n">
-        <v>6732464</v>
+        <v>6732415</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4841,29 +4841,34 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Födosökspår i flera lågor</t>
         </is>
       </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="b">
         <v>0</v>
@@ -4882,33 +4887,33 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125805740</t>
+          <t>https://artportalen.se/Sighting/136969495</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125812932</v>
+        <v>136969497</v>
       </c>
       <c r="B40" t="n">
-        <v>57953</v>
+        <v>58005</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4921,23 +4926,23 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>HACKMORA, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>512543</v>
+        <v>512420</v>
       </c>
       <c r="R40" t="n">
-        <v>6732471</v>
+        <v>6732419</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4961,29 +4966,34 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Påbörjat bobygge i gran som brutits av ca 3 m upp.</t>
         </is>
       </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="b">
         <v>0</v>
@@ -5002,33 +5012,33 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125812932</t>
+          <t>https://artportalen.se/Sighting/136969497</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125812971</v>
+        <v>136969507</v>
       </c>
       <c r="B41" t="n">
-        <v>57953</v>
+        <v>58005</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5047,17 +5057,17 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>HACKMORA, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>512539</v>
+        <v>512477</v>
       </c>
       <c r="R41" t="n">
-        <v>6732473</v>
+        <v>6732502</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5081,29 +5091,34 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>I GRANSUMPSKOG i två döda granar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="b">
         <v>0</v>
@@ -5122,33 +5137,33 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125812971</t>
+          <t>https://artportalen.se/Sighting/136969507</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125813330</v>
+        <v>136969522</v>
       </c>
       <c r="B42" t="n">
-        <v>57953</v>
+        <v>58005</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5156,28 +5171,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>HACKMORA, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>512524</v>
+        <v>512488</v>
       </c>
       <c r="R42" t="n">
-        <v>6732444</v>
+        <v>6732611</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5201,29 +5220,34 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ett bohål är kvar i delen av granen som är kvar efter brottet, minst tre bohål finns i delen som ligger på backen.</t>
         </is>
       </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="b">
         <v>0</v>
@@ -5242,13 +5266,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125813330</t>
+          <t>https://artportalen.se/Sighting/136969522</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125814282</v>
+        <v>125805740</v>
       </c>
       <c r="B43" t="n">
         <v>57953</v>
@@ -5277,16 +5301,24 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>512423</v>
+        <v>512523</v>
       </c>
       <c r="R43" t="n">
-        <v>6732722</v>
+        <v>6732464</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5318,7 +5350,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5328,14 +5360,14 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG43" t="b">
         <v>0</v>
@@ -5354,13 +5386,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125814282</t>
+          <t>https://artportalen.se/Sighting/125805740</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125816687</v>
+        <v>125812932</v>
       </c>
       <c r="B44" t="n">
         <v>57953</v>
@@ -5403,10 +5435,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>512426</v>
+        <v>512543</v>
       </c>
       <c r="R44" t="n">
-        <v>6732697</v>
+        <v>6732471</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5438,7 +5470,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5448,7 +5480,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5474,13 +5506,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125816687</t>
+          <t>https://artportalen.se/Sighting/125812932</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127784973</v>
+        <v>125812971</v>
       </c>
       <c r="B45" t="n">
         <v>57953</v>
@@ -5509,21 +5541,24 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hackmorkull, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>512564</v>
+        <v>512539</v>
       </c>
       <c r="R45" t="n">
-        <v>6732664</v>
+        <v>6732473</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5550,19 +5585,29 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG45" t="b">
         <v>0</v>
@@ -5570,27 +5615,27 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127784973</t>
+          <t>https://artportalen.se/Sighting/125812971</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131583623</v>
+        <v>125813330</v>
       </c>
       <c r="B46" t="n">
-        <v>57975</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5626,14 +5671,14 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>512410</v>
+        <v>512524</v>
       </c>
       <c r="R46" t="n">
-        <v>6732734</v>
+        <v>6732444</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5660,34 +5705,29 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>två granar</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG46" t="b">
         <v>0</v>
@@ -5700,22 +5740,22 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131583623</t>
+          <t>https://artportalen.se/Sighting/125813330</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133024788</v>
+        <v>125814282</v>
       </c>
       <c r="B47" t="n">
-        <v>57975</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5741,24 +5781,16 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>512546</v>
+        <v>512423</v>
       </c>
       <c r="R47" t="n">
-        <v>6732422</v>
+        <v>6732722</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5785,27 +5817,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:16</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Spår efter födosök på tre granar</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5825,68 +5852,68 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133024788</t>
+          <t>https://artportalen.se/Sighting/125814282</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126029719</v>
+        <v>125816687</v>
       </c>
       <c r="B48" t="n">
-        <v>57945</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hackmora, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>512451</v>
+        <v>512426</v>
       </c>
       <c r="R48" t="n">
-        <v>6732710</v>
+        <v>6732697</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5915,7 +5942,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5925,19 +5952,14 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Gråspetten satt i en av alla döda stående granar i närheten av rosentickorna.</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG48" t="b">
         <v>0</v>
@@ -5956,62 +5978,59 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126029719</t>
+          <t>https://artportalen.se/Sighting/125816687</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121401275</v>
+        <v>127784973</v>
       </c>
       <c r="B49" t="n">
-        <v>57141</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hackmora, Dlr</t>
+          <t>Hackmorkull, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>512405</v>
+        <v>512564</v>
       </c>
       <c r="R49" t="n">
-        <v>6732680</v>
+        <v>6732664</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6035,27 +6054,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>15:56</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Vacker kväll och jag hittade spillningen när jag skulle "ta lunch".</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6070,70 +6074,70 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121401275</t>
+          <t>https://artportalen.se/Sighting/127784973</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125974426</v>
+        <v>131583623</v>
       </c>
       <c r="B50" t="n">
-        <v>57141</v>
+        <v>57975</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>512516</v>
+        <v>512410</v>
       </c>
       <c r="R50" t="n">
-        <v>6732620</v>
+        <v>6732734</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6160,27 +6164,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>När jag stod i kanten mot en öppen yta, äng, hörde jag ett "tjäderbrak" i snåren på andra sidan ängen men jag hann bara se en skymt. Kan eventuellt varit samma hona som jag såg trekvart senare.</t>
+          <t>två granar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6200,69 +6204,65 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125974426</t>
+          <t>https://artportalen.se/Sighting/131583623</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125976030</v>
+        <v>133024788</v>
       </c>
       <c r="B51" t="n">
-        <v>57141</v>
+        <v>57975</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>512515</v>
+        <v>512546</v>
       </c>
       <c r="R51" t="n">
-        <v>6732684</v>
+        <v>6732422</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6289,27 +6289,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Uppflog, såg att det var en hona och kanske var det samma som jag hade sett</t>
+          <t>Spår efter födosök på tre granar</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6329,22 +6329,22 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125976030</t>
+          <t>https://artportalen.se/Sighting/133024788</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131583582</v>
+        <v>126029719</v>
       </c>
       <c r="B52" t="n">
-        <v>57162</v>
+        <v>57945</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6352,45 +6352,45 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>100110</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>512539</v>
+        <v>512451</v>
       </c>
       <c r="R52" t="n">
-        <v>6732405</v>
+        <v>6732710</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6414,22 +6414,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Gråspetten satt i en av alla döda stående granar i närheten av rosentickorna.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6449,22 +6454,22 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131583582</t>
+          <t>https://artportalen.se/Sighting/126029719</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127784955</v>
+        <v>121401275</v>
       </c>
       <c r="B53" t="n">
-        <v>4775</v>
+        <v>57141</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6472,42 +6477,45 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hackmorkull, Dlr</t>
+          <t>Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>512565</v>
+        <v>512405</v>
       </c>
       <c r="R53" t="n">
-        <v>6732458</v>
+        <v>6732680</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6531,12 +6539,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Vacker kväll och jag hittade spillningen när jag skulle "ta lunch".</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6551,27 +6574,27 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127784955</t>
+          <t>https://artportalen.se/Sighting/121401275</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121423787</v>
+        <v>125974426</v>
       </c>
       <c r="B54" t="n">
-        <v>5179</v>
+        <v>57141</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6579,34 +6602,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>512531</v>
+        <v>512516</v>
       </c>
       <c r="R54" t="n">
-        <v>6732485</v>
+        <v>6732620</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6633,12 +6664,27 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>När jag stod i kanten mot en öppen yta, äng, hörde jag ett "tjäderbrak" i snåren på andra sidan ängen men jag hann bara se en skymt. Kan eventuellt varit samma hona som jag såg trekvart senare.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6653,27 +6699,27 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121423787</t>
+          <t>https://artportalen.se/Sighting/125974426</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125964674</v>
+        <v>125976030</v>
       </c>
       <c r="B55" t="n">
-        <v>5179</v>
+        <v>57141</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6681,34 +6727,46 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>512459</v>
+        <v>512515</v>
       </c>
       <c r="R55" t="n">
-        <v>6732421</v>
+        <v>6732684</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6740,7 +6798,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6750,7 +6808,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>21:17</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Uppflog, såg att det var en hona och kanske var det samma som jag hade sett</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6776,16 +6839,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125964674</t>
+          <t>https://artportalen.se/Sighting/125976030</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121423765</v>
+        <v>131583582</v>
       </c>
       <c r="B56" t="n">
-        <v>57132</v>
+        <v>57162</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6793,21 +6856,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6815,7 +6878,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6825,10 +6888,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>512463</v>
+        <v>512539</v>
       </c>
       <c r="R56" t="n">
-        <v>6732461</v>
+        <v>6732405</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6855,12 +6918,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6875,27 +6948,27 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121423765</t>
+          <t>https://artportalen.se/Sighting/131583582</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121425289</v>
+        <v>127784955</v>
       </c>
       <c r="B57" t="n">
-        <v>57132</v>
+        <v>4775</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6903,38 +6976,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>102612</v>
+        <v>100299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmorkull, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>512643</v>
+        <v>512565</v>
       </c>
       <c r="R57" t="n">
-        <v>6732557</v>
+        <v>6732458</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6961,24 +7035,19 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>spillning, kändes som Järpe men kände mig osäker eftersom den var lite större än jag tänkt, se bild</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="b">
         <v>0</v>
@@ -6986,27 +7055,27 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121425289</t>
+          <t>https://artportalen.se/Sighting/127784955</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121426321</v>
+        <v>121423787</v>
       </c>
       <c r="B58" t="n">
-        <v>57132</v>
+        <v>5179</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7014,45 +7083,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>102612</v>
+        <v>100526</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>512598</v>
+        <v>512531</v>
       </c>
       <c r="R58" t="n">
-        <v>6732619</v>
+        <v>6732485</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7079,19 +7140,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7106,27 +7157,27 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121426321</t>
+          <t>https://artportalen.se/Sighting/121423787</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121177799</v>
+        <v>125964674</v>
       </c>
       <c r="B59" t="n">
-        <v>58327</v>
+        <v>5179</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7134,45 +7185,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103015</v>
+        <v>100526</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hackmorkull, Hackmorkull, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>512531</v>
+        <v>512459</v>
       </c>
       <c r="R59" t="n">
-        <v>6732409</v>
+        <v>6732421</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7196,27 +7239,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:32</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Jag har hört kungsfåglar på olika platser i området, varje gång jag besökt området.</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7242,16 +7280,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121177799</t>
+          <t>https://artportalen.se/Sighting/125964674</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121388880</v>
+        <v>121423765</v>
       </c>
       <c r="B60" t="n">
-        <v>58327</v>
+        <v>57132</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7259,16 +7297,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>102612</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7281,23 +7319,23 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hackmora, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>512611</v>
+        <v>512463</v>
       </c>
       <c r="R60" t="n">
-        <v>6732496</v>
+        <v>6732461</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7321,22 +7359,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:22</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:22</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7351,27 +7379,27 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121388880</t>
+          <t>https://artportalen.se/Sighting/121423765</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121388881</v>
+        <v>121425289</v>
       </c>
       <c r="B61" t="n">
-        <v>58327</v>
+        <v>57132</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7379,16 +7407,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103015</v>
+        <v>102612</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7399,25 +7427,21 @@
       <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hackmora, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>512593</v>
+        <v>512643</v>
       </c>
       <c r="R61" t="n">
-        <v>6732493</v>
+        <v>6732557</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7441,34 +7465,24 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>13:55</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>13:55</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Den lät som kungsfåglar låter på hösten.</t>
+          <t>spillning, kändes som Järpe men kände mig osäker eftersom den var lite större än jag tänkt, se bild</t>
         </is>
       </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG61" t="b">
         <v>0</v>
@@ -7476,27 +7490,27 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121388881</t>
+          <t>https://artportalen.se/Sighting/121425289</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125810285</v>
+        <v>121426321</v>
       </c>
       <c r="B62" t="n">
-        <v>58327</v>
+        <v>57132</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7504,16 +7518,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103015</v>
+        <v>102612</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7524,21 +7538,25 @@
       <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>512560</v>
+        <v>512598</v>
       </c>
       <c r="R62" t="n">
-        <v>6732515</v>
+        <v>6732619</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7562,27 +7580,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>19:18</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Osäker på antal</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7602,19 +7615,19 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125810285</t>
+          <t>https://artportalen.se/Sighting/121426321</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125973632</v>
+        <v>121177799</v>
       </c>
       <c r="B63" t="n">
         <v>58327</v>
@@ -7642,28 +7655,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmorkull, Hackmorkull, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>512495</v>
+        <v>512531</v>
       </c>
       <c r="R63" t="n">
-        <v>6732470</v>
+        <v>6732409</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7687,27 +7700,27 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Bakom trädskärmen finns ett blötare område med vattenklöver och fläcknycklar.</t>
+          <t>Jag har hört kungsfåglar på olika platser i området, varje gång jag besökt området.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7733,38 +7746,38 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125973632</t>
+          <t>https://artportalen.se/Sighting/121177799</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121388879</v>
+        <v>121388880</v>
       </c>
       <c r="B64" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7830,11 +7843,6 @@
           <t>14:22</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Den lät som talltitor låter på hösten</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7858,38 +7866,38 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121388879</t>
+          <t>https://artportalen.se/Sighting/121388880</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131583625</v>
+        <v>121388881</v>
       </c>
       <c r="B65" t="n">
-        <v>58136</v>
+        <v>58327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7897,23 +7905,23 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>512465</v>
+        <v>512593</v>
       </c>
       <c r="R65" t="n">
-        <v>6732548</v>
+        <v>6732493</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7937,27 +7945,27 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>miljöbild</t>
+          <t>Den lät som kungsfåglar låter på hösten.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7977,57 +7985,61 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131583625</t>
+          <t>https://artportalen.se/Sighting/121388881</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126586787</v>
+        <v>125810285</v>
       </c>
       <c r="B66" t="n">
-        <v>56522</v>
+        <v>58327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>206004</v>
+        <v>103015</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>512494</v>
+        <v>512560</v>
       </c>
       <c r="R66" t="n">
-        <v>6732599</v>
+        <v>6732515</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8054,22 +8066,27 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Osäker på antal</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8089,22 +8106,22 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126586787</t>
+          <t>https://artportalen.se/Sighting/125810285</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125969156</v>
+        <v>125973632</v>
       </c>
       <c r="B67" t="n">
-        <v>58817</v>
+        <v>58327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8112,36 +8129,31 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>208249</v>
+        <v>103015</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8149,13 +8161,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>512467</v>
+        <v>512495</v>
       </c>
       <c r="R67" t="n">
-        <v>6732466</v>
+        <v>6732470</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8184,7 +8196,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8194,12 +8206,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>En liten ljusbrun groda med mörkare fläckar och slank kropp.  Jag såg egentligen två på två olika ställen men jag noterade bara koordinaterna på den ena eftersom jag inte hann ta något foto på den. När jag såg en till rapporterade jag den eftersom jag tycker att grodor är viktiga, men jag hann inte ta någon bild på den heller innan den försvann under blåbärsriset.</t>
+          <t>Bakom trädskärmen finns ett blötare område med vattenklöver och fläcknycklar.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8208,7 +8220,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8226,67 +8237,62 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125969156</t>
+          <t>https://artportalen.se/Sighting/125973632</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125971105</v>
+        <v>121388879</v>
       </c>
       <c r="B68" t="n">
-        <v>58817</v>
+        <v>58114</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>208249</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>512473</v>
+        <v>512611</v>
       </c>
       <c r="R68" t="n">
-        <v>6732483</v>
+        <v>6732496</v>
       </c>
       <c r="S68" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8310,27 +8316,27 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>En liten slank ljusbrun groda med mörka fläckar.</t>
+          <t>Den lät som talltitor låter på hösten</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8339,7 +8345,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8357,60 +8362,59 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125971105</t>
+          <t>https://artportalen.se/Sighting/121388879</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126587009</v>
+        <v>131583625</v>
       </c>
       <c r="B69" t="n">
-        <v>58817</v>
+        <v>58136</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>208249</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>512448</v>
+        <v>512465</v>
       </c>
       <c r="R69" t="n">
-        <v>6732674</v>
+        <v>6732548</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8437,27 +8441,27 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Där det rinner vatten efter stigen strax före Hackmorkull. Det finns säkert fler än två, i avverkningsanmält område.</t>
+          <t>miljöbild</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8466,7 +8470,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8484,16 +8487,16 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126587009</t>
+          <t>https://artportalen.se/Sighting/131583625</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125807286</v>
+        <v>136969512</v>
       </c>
       <c r="B70" t="n">
-        <v>99035</v>
+        <v>58164</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8501,49 +8504,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219790</v>
+        <v>103023</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>HACKMORA, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>512607</v>
+        <v>512485</v>
       </c>
       <c r="R70" t="n">
-        <v>6732455</v>
+        <v>6732558</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8567,22 +8558,27 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>ingen bild</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8591,7 +8587,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8609,63 +8604,51 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125807286</t>
+          <t>https://artportalen.se/Sighting/136969512</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125809958</v>
+        <v>126586787</v>
       </c>
       <c r="B71" t="n">
-        <v>99035</v>
+        <v>56522</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219790</v>
+        <v>206004</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>512558</v>
+        <v>512494</v>
       </c>
       <c r="R71" t="n">
-        <v>6732515</v>
+        <v>6732599</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8692,22 +8675,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8716,7 +8699,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8728,22 +8710,22 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125809958</t>
+          <t>https://artportalen.se/Sighting/126586787</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125810466</v>
+        <v>125969156</v>
       </c>
       <c r="B72" t="n">
-        <v>99035</v>
+        <v>58817</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8751,49 +8733,50 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219790</v>
+        <v>208249</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>512560</v>
+        <v>512467</v>
       </c>
       <c r="R72" t="n">
-        <v>6732515</v>
+        <v>6732466</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8817,22 +8800,27 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>En liten ljusbrun groda med mörkare fläckar och slank kropp.  Jag såg egentligen två på två olika ställen men jag noterade bara koordinaterna på den ena eftersom jag inte hann ta något foto på den. När jag såg en till rapporterade jag den eftersom jag tycker att grodor är viktiga, men jag hann inte ta någon bild på den heller innan den försvann under blåbärsriset.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8859,16 +8847,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125810466</t>
+          <t>https://artportalen.se/Sighting/125969156</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125812392</v>
+        <v>125971105</v>
       </c>
       <c r="B73" t="n">
-        <v>99035</v>
+        <v>58817</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8876,37 +8864,50 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219790</v>
+        <v>208249</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>512543</v>
+        <v>512473</v>
       </c>
       <c r="R73" t="n">
-        <v>6732510</v>
+        <v>6732483</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8930,22 +8931,27 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>En liten slank ljusbrun groda med mörka fläckar.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8954,6 +8960,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8971,16 +8978,16 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125812392</t>
+          <t>https://artportalen.se/Sighting/125971105</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125813513</v>
+        <v>126587009</v>
       </c>
       <c r="B74" t="n">
-        <v>99035</v>
+        <v>58817</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8988,34 +8995,43 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219790</v>
+        <v>208249</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>512505</v>
+        <v>512448</v>
       </c>
       <c r="R74" t="n">
-        <v>6732477</v>
+        <v>6732674</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9042,22 +9058,27 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Där det rinner vatten efter stigen strax före Hackmorkull. Det finns säkert fler än två, i avverkningsanmält område.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9066,6 +9087,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9077,19 +9099,19 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125813513</t>
+          <t>https://artportalen.se/Sighting/126587009</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125968512</v>
+        <v>125807286</v>
       </c>
       <c r="B75" t="n">
         <v>99035</v>
@@ -9119,30 +9141,30 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>512462</v>
+        <v>512607</v>
       </c>
       <c r="R75" t="n">
-        <v>6732477</v>
+        <v>6732455</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9166,22 +9188,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9208,13 +9230,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125968512</t>
+          <t>https://artportalen.se/Sighting/125807286</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125969094</v>
+        <v>125809958</v>
       </c>
       <c r="B76" t="n">
         <v>99035</v>
@@ -9242,17 +9264,29 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>512467</v>
+        <v>512558</v>
       </c>
       <c r="R76" t="n">
-        <v>6732466</v>
+        <v>6732515</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9279,22 +9313,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9303,6 +9337,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -9320,13 +9355,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125969094</t>
+          <t>https://artportalen.se/Sighting/125809958</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125970965</v>
+        <v>125810466</v>
       </c>
       <c r="B77" t="n">
         <v>99035</v>
@@ -9354,20 +9389,32 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>512473</v>
+        <v>512560</v>
       </c>
       <c r="R77" t="n">
-        <v>6732483</v>
+        <v>6732515</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9391,27 +9438,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>18:36</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Inom en radie på fem meter 100st</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9420,6 +9462,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9437,13 +9480,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125970965</t>
+          <t>https://artportalen.se/Sighting/125810466</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125971419</v>
+        <v>125812392</v>
       </c>
       <c r="B78" t="n">
         <v>99035</v>
@@ -9474,17 +9517,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>512481</v>
+        <v>512543</v>
       </c>
       <c r="R78" t="n">
-        <v>6732503</v>
+        <v>6732510</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9508,27 +9551,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>18:53</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Kärrviol frånen</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9554,16 +9592,16 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125971419</t>
+          <t>https://artportalen.se/Sighting/125812392</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125810185</v>
+        <v>125813513</v>
       </c>
       <c r="B79" t="n">
-        <v>99022</v>
+        <v>99035</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9571,46 +9609,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>512554</v>
+        <v>512505</v>
       </c>
       <c r="R79" t="n">
-        <v>6732516</v>
+        <v>6732477</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9642,7 +9668,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9652,12 +9678,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>19:13</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Svårt att säga hur många man ser ju bara dem med blomstänglar.</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9666,7 +9687,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -9684,16 +9704,16 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125810185</t>
+          <t>https://artportalen.se/Sighting/125813513</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>134163552</v>
+        <v>125968512</v>
       </c>
       <c r="B80" t="n">
-        <v>111153</v>
+        <v>99035</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9701,37 +9721,49 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220240</v>
+        <v>219790</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Hackmorkull, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>512423</v>
+        <v>512462</v>
       </c>
       <c r="R80" t="n">
-        <v>6732700</v>
+        <v>6732477</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9755,27 +9787,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>vindfälle tall, översållat m linnea</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9784,6 +9811,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9801,60 +9829,51 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134163552</t>
+          <t>https://artportalen.se/Sighting/125968512</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121423764</v>
+        <v>125969094</v>
       </c>
       <c r="B81" t="n">
-        <v>99118</v>
+        <v>99035</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>512489</v>
+        <v>512467</v>
       </c>
       <c r="R81" t="n">
-        <v>6732468</v>
+        <v>6732466</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9881,12 +9900,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9901,73 +9930,65 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121423764</t>
+          <t>https://artportalen.se/Sighting/125969094</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121425292</v>
+        <v>125970965</v>
       </c>
       <c r="B82" t="n">
-        <v>99118</v>
+        <v>99035</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>512561</v>
+        <v>512473</v>
       </c>
       <c r="R82" t="n">
-        <v>6732464</v>
+        <v>6732483</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9991,17 +10012,27 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>varav ca 20 med blomställning</t>
+          <t>Inom en radie på fem meter 100st</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10010,88 +10041,71 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Beke Regelin, Irina Röjås</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121425292</t>
+          <t>https://artportalen.se/Sighting/125970965</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125811035</v>
+        <v>125971419</v>
       </c>
       <c r="B83" t="n">
-        <v>99118</v>
+        <v>99035</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>512578</v>
+        <v>512481</v>
       </c>
       <c r="R83" t="n">
-        <v>6732520</v>
+        <v>6732503</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10115,27 +10129,27 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Minst 50 Flera med blomstänglar.</t>
+          <t>Kärrviol frånen</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10144,7 +10158,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -10162,43 +10175,43 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125811035</t>
+          <t>https://artportalen.se/Sighting/125971419</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125967830</v>
+        <v>125810185</v>
       </c>
       <c r="B84" t="n">
-        <v>99118</v>
+        <v>99022</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10206,26 +10219,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>512459</v>
+        <v>512554</v>
       </c>
       <c r="R84" t="n">
-        <v>6732486</v>
+        <v>6732516</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10249,22 +10258,27 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Svårt att säga hur många man ser ju bara dem med blomstänglar.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10291,58 +10305,54 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125967830</t>
+          <t>https://artportalen.se/Sighting/125810185</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125969749</v>
+        <v>134163552</v>
       </c>
       <c r="B85" t="n">
-        <v>99118</v>
+        <v>111153</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmorkull, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>512472</v>
+        <v>512423</v>
       </c>
       <c r="R85" t="n">
-        <v>6732471</v>
+        <v>6732700</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10366,22 +10376,27 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>vindfälle tall, översållat m linnea</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10390,7 +10405,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -10408,13 +10422,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125969749</t>
+          <t>https://artportalen.se/Sighting/134163552</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125970447</v>
+        <v>121423764</v>
       </c>
       <c r="B86" t="n">
         <v>99118</v>
@@ -10444,7 +10458,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10452,26 +10466,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>512475</v>
+        <v>512489</v>
       </c>
       <c r="R86" t="n">
-        <v>6732479</v>
+        <v>6732468</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10495,27 +10502,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>18:16</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>18:16</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Däremot fanns inga blomstänglar just här.</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10524,31 +10516,30 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125970447</t>
+          <t>https://artportalen.se/Sighting/121423764</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125972943</v>
+        <v>121425292</v>
       </c>
       <c r="B87" t="n">
         <v>99118</v>
@@ -10578,30 +10569,26 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>512495</v>
+        <v>512561</v>
       </c>
       <c r="R87" t="n">
-        <v>6732470</v>
+        <v>6732464</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10625,27 +10612,17 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>19:47</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>19:47</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>uppskattat antal.</t>
+          <t>varav ca 20 med blomställning</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10661,66 +10638,78 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Beke Regelin, Irina Röjås</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125972943</t>
+          <t>https://artportalen.se/Sighting/121425292</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127085273</v>
+        <v>125811035</v>
       </c>
       <c r="B88" t="n">
-        <v>102240</v>
+        <v>99118</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221235</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Hackmorkull, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>512526</v>
+        <v>512578</v>
       </c>
       <c r="R88" t="n">
-        <v>6732574</v>
+        <v>6732520</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10747,12 +10736,27 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>19:37</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Minst 50 Flera med blomstänglar.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10768,54 +10772,54 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127085273</t>
+          <t>https://artportalen.se/Sighting/125811035</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125810697</v>
+        <v>125967830</v>
       </c>
       <c r="B89" t="n">
-        <v>106229</v>
+        <v>99118</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10823,22 +10827,26 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>512560</v>
+        <v>512459</v>
       </c>
       <c r="R89" t="n">
-        <v>6732515</v>
+        <v>6732486</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10862,27 +10870,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>19:28</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Så liten, så skör och så vacker!</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10909,66 +10912,58 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125810697</t>
+          <t>https://artportalen.se/Sighting/125967830</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125811364</v>
+        <v>125969749</v>
       </c>
       <c r="B90" t="n">
-        <v>106229</v>
+        <v>99118</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>512579</v>
+        <v>512472</v>
       </c>
       <c r="R90" t="n">
-        <v>6732525</v>
+        <v>6732471</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10992,27 +10987,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>19:48</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Uppskattat antal, blommande, knopp och plantor utan.</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11039,54 +11029,70 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125811364</t>
+          <t>https://artportalen.se/Sighting/125969749</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125812445</v>
+        <v>125970447</v>
       </c>
       <c r="B91" t="n">
-        <v>106229</v>
+        <v>99118</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>512543</v>
+        <v>512475</v>
       </c>
       <c r="R91" t="n">
-        <v>6732510</v>
+        <v>6732479</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11110,22 +11116,27 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Däremot fanns inga blomstänglar just här.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11134,6 +11145,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -11151,48 +11163,48 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125812445</t>
+          <t>https://artportalen.se/Sighting/125970447</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121179502</v>
+        <v>125972943</v>
       </c>
       <c r="B92" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -11200,17 +11212,17 @@
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Hackmorkull, Hackmorkull, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>512532</v>
+        <v>512495</v>
       </c>
       <c r="R92" t="n">
-        <v>6732598</v>
+        <v>6732470</v>
       </c>
       <c r="S92" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11234,27 +11246,27 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>10x3 m, uppskattat område</t>
+          <t>uppskattat antal.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11281,38 +11293,38 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121179502</t>
+          <t>https://artportalen.se/Sighting/125972943</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121399884</v>
+        <v>127085273</v>
       </c>
       <c r="B93" t="n">
-        <v>97983</v>
+        <v>102240</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221945</v>
+        <v>221235</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11322,17 +11334,17 @@
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Hackmora, Dlr</t>
+          <t>Hackmorkull, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>512569</v>
+        <v>512526</v>
       </c>
       <c r="R93" t="n">
-        <v>6732458</v>
+        <v>6732574</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11356,22 +11368,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>15:09</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>15:09</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11387,27 +11389,27 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121399884</t>
+          <t>https://artportalen.se/Sighting/127085273</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121425291</v>
+        <v>125810697</v>
       </c>
       <c r="B94" t="n">
-        <v>97983</v>
+        <v>106229</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11415,34 +11417,46 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>512552</v>
+        <v>512560</v>
       </c>
       <c r="R94" t="n">
-        <v>6732510</v>
+        <v>6732515</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11469,12 +11483,27 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Så liten, så skör och så vacker!</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11483,33 +11512,34 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121425291</t>
+          <t>https://artportalen.se/Sighting/125810697</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125971792</v>
+        <v>125811364</v>
       </c>
       <c r="B95" t="n">
-        <v>97983</v>
+        <v>106229</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11517,31 +11547,31 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -11549,17 +11579,17 @@
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>512451</v>
+        <v>512579</v>
       </c>
       <c r="R95" t="n">
-        <v>6732445</v>
+        <v>6732525</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11583,27 +11613,27 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Minst sex mindre grupper på en mindre yta.</t>
+          <t>Uppskattat antal, blommande, knopp och plantor utan.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11630,16 +11660,16 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125971792</t>
+          <t>https://artportalen.se/Sighting/125811364</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126586715</v>
+        <v>125812445</v>
       </c>
       <c r="B96" t="n">
-        <v>97983</v>
+        <v>106229</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11647,46 +11677,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>512493</v>
+        <v>512543</v>
       </c>
       <c r="R96" t="n">
-        <v>6732582</v>
+        <v>6732510</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11713,27 +11731,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Betespräglad fäbodskog, olika ormbunkar, ormbär, ekorrbär, asp, rönn, björk, gran</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11742,7 +11755,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -11754,19 +11766,19 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126586715</t>
+          <t>https://artportalen.se/Sighting/125812445</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127085227</v>
+        <v>121179502</v>
       </c>
       <c r="B97" t="n">
         <v>97983</v>
@@ -11794,20 +11806,32 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Hackmorkull, Dlr</t>
+          <t>Hackmorkull, Hackmorkull, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>512526</v>
+        <v>512532</v>
       </c>
       <c r="R97" t="n">
-        <v>6732591</v>
+        <v>6732598</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11831,12 +11855,27 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>10x3 m, uppskattat område</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11845,33 +11884,34 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127085227</t>
+          <t>https://artportalen.se/Sighting/121179502</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125809649</v>
+        <v>121399884</v>
       </c>
       <c r="B98" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11879,49 +11919,41 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>512552</v>
+        <v>512569</v>
       </c>
       <c r="R98" t="n">
-        <v>6732505</v>
+        <v>6732458</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11945,27 +11977,22 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>18:56</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Några i blom</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11992,16 +12019,16 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125809649</t>
+          <t>https://artportalen.se/Sighting/121399884</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125809802</v>
+        <v>121425291</v>
       </c>
       <c r="B99" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12009,46 +12036,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>512547</v>
+        <v>512552</v>
       </c>
       <c r="R99" t="n">
-        <v>6732517</v>
+        <v>6732510</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12075,22 +12090,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>19:02</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>19:02</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12099,34 +12104,33 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125809802</t>
+          <t>https://artportalen.se/Sighting/121425291</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125810907</v>
+        <v>125971792</v>
       </c>
       <c r="B100" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12134,31 +12138,31 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -12166,17 +12170,17 @@
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>512578</v>
+        <v>512451</v>
       </c>
       <c r="R100" t="n">
-        <v>6732520</v>
+        <v>6732445</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12200,27 +12204,27 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Några i blom och några utan blommor</t>
+          <t>Minst sex mindre grupper på en mindre yta.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12247,16 +12251,16 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125810907</t>
+          <t>https://artportalen.se/Sighting/125971792</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125812085</v>
+        <v>126586715</v>
       </c>
       <c r="B101" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12264,38 +12268,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
@@ -12304,10 +12304,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>512564</v>
+        <v>512493</v>
       </c>
       <c r="R101" t="n">
-        <v>6732513</v>
+        <v>6732582</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12334,27 +12334,27 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Så små och så sköra. De kan aldrig överleva en avverkning och inte marken de växter i heller. Det finns en hel del blad men alla plantor blommar inte.</t>
+          <t>Betespräglad fäbodskog, olika ormbunkar, ormbär, ekorrbär, asp, rönn, björk, gran</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12375,22 +12375,22 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125812085</t>
+          <t>https://artportalen.se/Sighting/126586715</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125968150</v>
+        <v>127085227</v>
       </c>
       <c r="B102" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12398,49 +12398,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmorkull, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>512450</v>
+        <v>512526</v>
       </c>
       <c r="R102" t="n">
-        <v>6732474</v>
+        <v>6732591</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12464,27 +12452,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>16:49</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>16:49</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Några blommade. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12493,31 +12466,30 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125968150</t>
+          <t>https://artportalen.se/Sighting/127085227</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125969726</v>
+        <v>125809649</v>
       </c>
       <c r="B103" t="n">
         <v>99140</v>
@@ -12547,7 +12519,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12555,26 +12527,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>512469</v>
+        <v>512552</v>
       </c>
       <c r="R103" t="n">
-        <v>6732470</v>
+        <v>6732505</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12598,27 +12566,27 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
+          <t>Några i blom</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12645,13 +12613,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125969726</t>
+          <t>https://artportalen.se/Sighting/125809649</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125970625</v>
+        <v>125809802</v>
       </c>
       <c r="B104" t="n">
         <v>99140</v>
@@ -12681,7 +12649,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12689,26 +12657,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>512475</v>
+        <v>512547</v>
       </c>
       <c r="R104" t="n">
-        <v>6732479</v>
+        <v>6732517</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12732,27 +12696,22 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>18:23</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Jag hade redan registrerat 100 när jag såg att de var flera. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12779,13 +12738,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125970625</t>
+          <t>https://artportalen.se/Sighting/125809802</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125971336</v>
+        <v>125810907</v>
       </c>
       <c r="B105" t="n">
         <v>99140</v>
@@ -12815,7 +12774,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -12828,17 +12787,17 @@
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>512484</v>
+        <v>512578</v>
       </c>
       <c r="R105" t="n">
-        <v>6732491</v>
+        <v>6732520</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12862,27 +12821,27 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
+          <t>Några i blom och några utan blommor</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12909,13 +12868,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125971336</t>
+          <t>https://artportalen.se/Sighting/125810907</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125971458</v>
+        <v>125812085</v>
       </c>
       <c r="B106" t="n">
         <v>99140</v>
@@ -12943,9 +12902,21 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
@@ -12954,13 +12925,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>512481</v>
+        <v>512564</v>
       </c>
       <c r="R106" t="n">
-        <v>6732503</v>
+        <v>6732513</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12984,27 +12955,27 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
+          <t>Så små och så sköra. De kan aldrig överleva en avverkning och inte marken de växter i heller. Det finns en hel del blad men alla plantor blommar inte.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13031,13 +13002,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125971458</t>
+          <t>https://artportalen.se/Sighting/125812085</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125972442</v>
+        <v>125968150</v>
       </c>
       <c r="B107" t="n">
         <v>99140</v>
@@ -13067,7 +13038,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -13075,11 +13046,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
@@ -13088,10 +13055,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>512481</v>
+        <v>512450</v>
       </c>
       <c r="R107" t="n">
-        <v>6732473</v>
+        <v>6732474</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -13123,7 +13090,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13133,12 +13100,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
+          <t>Några blommade. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13165,16 +13132,16 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125972442</t>
+          <t>https://artportalen.se/Sighting/125968150</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121423789</v>
+        <v>125969726</v>
       </c>
       <c r="B108" t="n">
-        <v>101326</v>
+        <v>99140</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13182,37 +13149,53 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>512635</v>
+        <v>512469</v>
       </c>
       <c r="R108" t="n">
-        <v>6732571</v>
+        <v>6732470</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13236,12 +13219,27 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13250,33 +13248,34 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121423789</t>
+          <t>https://artportalen.se/Sighting/125969726</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121423790</v>
+        <v>125970625</v>
       </c>
       <c r="B109" t="n">
-        <v>101326</v>
+        <v>99140</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13284,37 +13283,53 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>512628</v>
+        <v>512475</v>
       </c>
       <c r="R109" t="n">
-        <v>6732540</v>
+        <v>6732479</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13338,12 +13353,27 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Jag hade redan registrerat 100 när jag såg att de var flera. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13352,33 +13382,34 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121423790</t>
+          <t>https://artportalen.se/Sighting/125970625</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121423791</v>
+        <v>125971336</v>
       </c>
       <c r="B110" t="n">
-        <v>101326</v>
+        <v>99140</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13386,37 +13417,49 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>512638</v>
+        <v>512484</v>
       </c>
       <c r="R110" t="n">
-        <v>6732516</v>
+        <v>6732491</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13440,12 +13483,27 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13454,33 +13512,34 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121423791</t>
+          <t>https://artportalen.se/Sighting/125971336</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121423792</v>
+        <v>125971458</v>
       </c>
       <c r="B111" t="n">
-        <v>101326</v>
+        <v>99140</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13488,37 +13547,41 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>512628</v>
+        <v>512481</v>
       </c>
       <c r="R111" t="n">
-        <v>6732517</v>
+        <v>6732503</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13542,12 +13605,27 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13556,33 +13634,34 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121423792</t>
+          <t>https://artportalen.se/Sighting/125971458</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121425050</v>
+        <v>125972442</v>
       </c>
       <c r="B112" t="n">
-        <v>101326</v>
+        <v>99140</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13590,41 +13669,53 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>512609</v>
+        <v>512481</v>
       </c>
       <c r="R112" t="n">
-        <v>6732541</v>
+        <v>6732473</v>
       </c>
       <c r="S112" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13648,22 +13739,27 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13684,19 +13780,19 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121425050</t>
+          <t>https://artportalen.se/Sighting/125972442</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121425051</v>
+        <v>121423789</v>
       </c>
       <c r="B113" t="n">
         <v>101326</v>
@@ -13725,23 +13821,19 @@
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>512639</v>
+        <v>512635</v>
       </c>
       <c r="R113" t="n">
-        <v>6732526</v>
+        <v>6732571</v>
       </c>
       <c r="S113" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13768,52 +13860,41 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121425051</t>
+          <t>https://artportalen.se/Sighting/121423789</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121425052</v>
+        <v>121423790</v>
       </c>
       <c r="B114" t="n">
         <v>101326</v>
@@ -13842,23 +13923,19 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>512626</v>
+        <v>512628</v>
       </c>
       <c r="R114" t="n">
-        <v>6732514</v>
+        <v>6732540</v>
       </c>
       <c r="S114" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13885,52 +13962,41 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121425052</t>
+          <t>https://artportalen.se/Sighting/121423790</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127784976</v>
+        <v>121423791</v>
       </c>
       <c r="B115" t="n">
         <v>101326</v>
@@ -13961,14 +14027,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Hackmorkull, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>512517</v>
+        <v>512638</v>
       </c>
       <c r="R115" t="n">
-        <v>6732569</v>
+        <v>6732516</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13995,12 +14061,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14020,22 +14086,22 @@
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127784976</t>
+          <t>https://artportalen.se/Sighting/121423791</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121426318</v>
+        <v>121423792</v>
       </c>
       <c r="B116" t="n">
-        <v>97985</v>
+        <v>101326</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14043,37 +14109,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>224363</v>
+        <v>222498</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>512584</v>
+        <v>512628</v>
       </c>
       <c r="R116" t="n">
-        <v>6732486</v>
+        <v>6732517</v>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14100,44 +14166,716 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121423792</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>121425050</v>
+      </c>
+      <c r="B117" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>512609</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6732541</v>
+      </c>
+      <c r="S117" t="n">
+        <v>15</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121425050</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>121425051</v>
+      </c>
+      <c r="B118" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>512639</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6732526</v>
+      </c>
+      <c r="S118" t="n">
+        <v>15</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121425051</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>121425052</v>
+      </c>
+      <c r="B119" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>512626</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6732514</v>
+      </c>
+      <c r="S119" t="n">
+        <v>15</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121425052</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>127784976</v>
+      </c>
+      <c r="B120" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Hackmorkull, Dlr</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>512517</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6732569</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784976</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>136969516</v>
+      </c>
+      <c r="B121" t="n">
+        <v>99630</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>HACKMORA, Dlr</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>512496</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6732586</v>
+      </c>
+      <c r="S121" t="n">
+        <v>5</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>3100 bären</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136969516</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121426318</v>
+      </c>
+      <c r="B122" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>512584</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6732486</v>
+      </c>
+      <c r="S122" t="n">
+        <v>15</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF122" t="inlineStr"/>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/121426318</t>
         </is>
@@ -14260,6 +14998,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8191-2026 artfynd.xlsx
+++ b/artfynd/A 8191-2026 artfynd.xlsx
@@ -14656,7 +14656,7 @@
         <v>136969516</v>
       </c>
       <c r="B121" t="n">
-        <v>99630</v>
+        <v>99636</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 8191-2026 artfynd.xlsx
+++ b/artfynd/A 8191-2026 artfynd.xlsx
@@ -14656,7 +14656,7 @@
         <v>136969516</v>
       </c>
       <c r="B121" t="n">
-        <v>99636</v>
+        <v>99638</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 8191-2026 artfynd.xlsx
+++ b/artfynd/A 8191-2026 artfynd.xlsx
@@ -14656,7 +14656,7 @@
         <v>136969516</v>
       </c>
       <c r="B121" t="n">
-        <v>99638</v>
+        <v>99639</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 8191-2026 artfynd.xlsx
+++ b/artfynd/A 8191-2026 artfynd.xlsx
@@ -14656,7 +14656,7 @@
         <v>136969516</v>
       </c>
       <c r="B121" t="n">
-        <v>99639</v>
+        <v>99645</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 8191-2026 artfynd.xlsx
+++ b/artfynd/A 8191-2026 artfynd.xlsx
@@ -14656,7 +14656,7 @@
         <v>136969516</v>
       </c>
       <c r="B121" t="n">
-        <v>99645</v>
+        <v>99649</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 8191-2026 artfynd.xlsx
+++ b/artfynd/A 8191-2026 artfynd.xlsx
@@ -14656,7 +14656,7 @@
         <v>136969516</v>
       </c>
       <c r="B121" t="n">
-        <v>99649</v>
+        <v>99651</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 8191-2026 artfynd.xlsx
+++ b/artfynd/A 8191-2026 artfynd.xlsx
@@ -14656,7 +14656,7 @@
         <v>136969516</v>
       </c>
       <c r="B121" t="n">
-        <v>99651</v>
+        <v>99653</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 8191-2026 artfynd.xlsx
+++ b/artfynd/A 8191-2026 artfynd.xlsx
@@ -4771,7 +4771,7 @@
         <v>136969495</v>
       </c>
       <c r="B39" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         <v>136969497</v>
       </c>
       <c r="B40" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>136969507</v>
       </c>
       <c r="B41" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>136969522</v>
       </c>
       <c r="B42" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>136969512</v>
       </c>
       <c r="B70" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -14656,7 +14656,7 @@
         <v>136969516</v>
       </c>
       <c r="B121" t="n">
-        <v>99653</v>
+        <v>99666</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 8191-2026 artfynd.xlsx
+++ b/artfynd/A 8191-2026 artfynd.xlsx
@@ -4771,7 +4771,7 @@
         <v>136969495</v>
       </c>
       <c r="B39" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         <v>136969497</v>
       </c>
       <c r="B40" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>136969507</v>
       </c>
       <c r="B41" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>136969522</v>
       </c>
       <c r="B42" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>136969512</v>
       </c>
       <c r="B70" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -14656,7 +14656,7 @@
         <v>136969516</v>
       </c>
       <c r="B121" t="n">
-        <v>99666</v>
+        <v>99668</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 8191-2026 artfynd.xlsx
+++ b/artfynd/A 8191-2026 artfynd.xlsx
@@ -4799,11 +4799,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4924,11 +4920,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5049,11 +5041,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5178,11 +5166,7 @@
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>

--- a/artfynd/A 8191-2026 artfynd.xlsx
+++ b/artfynd/A 8191-2026 artfynd.xlsx
@@ -14640,7 +14640,7 @@
         <v>136969516</v>
       </c>
       <c r="B121" t="n">
-        <v>99668</v>
+        <v>99671</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 8191-2026 artfynd.xlsx
+++ b/artfynd/A 8191-2026 artfynd.xlsx
@@ -4771,7 +4771,7 @@
         <v>136969495</v>
       </c>
       <c r="B39" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>136969497</v>
       </c>
       <c r="B40" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>136969507</v>
       </c>
       <c r="B41" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>136969522</v>
       </c>
       <c r="B42" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>136969512</v>
       </c>
       <c r="B70" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>136969516</v>
       </c>
       <c r="B121" t="n">
-        <v>99671</v>
+        <v>99681</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 8191-2026 artfynd.xlsx
+++ b/artfynd/A 8191-2026 artfynd.xlsx
@@ -14640,7 +14640,7 @@
         <v>136969516</v>
       </c>
       <c r="B121" t="n">
-        <v>99681</v>
+        <v>99682</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 8191-2026 artfynd.xlsx
+++ b/artfynd/A 8191-2026 artfynd.xlsx
@@ -4771,7 +4771,7 @@
         <v>136969495</v>
       </c>
       <c r="B39" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>136969497</v>
       </c>
       <c r="B40" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>136969507</v>
       </c>
       <c r="B41" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>136969522</v>
       </c>
       <c r="B42" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>136969512</v>
       </c>
       <c r="B70" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>136969516</v>
       </c>
       <c r="B121" t="n">
-        <v>99682</v>
+        <v>99687</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 8191-2026 artfynd.xlsx
+++ b/artfynd/A 8191-2026 artfynd.xlsx
@@ -14640,7 +14640,7 @@
         <v>136969516</v>
       </c>
       <c r="B121" t="n">
-        <v>99687</v>
+        <v>99690</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 8191-2026 artfynd.xlsx
+++ b/artfynd/A 8191-2026 artfynd.xlsx
@@ -4771,7 +4771,7 @@
         <v>136969495</v>
       </c>
       <c r="B39" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>136969497</v>
       </c>
       <c r="B40" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>136969507</v>
       </c>
       <c r="B41" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>136969522</v>
       </c>
       <c r="B42" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>136969512</v>
       </c>
       <c r="B70" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>136969516</v>
       </c>
       <c r="B121" t="n">
-        <v>99690</v>
+        <v>99696</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 8191-2026 artfynd.xlsx
+++ b/artfynd/A 8191-2026 artfynd.xlsx
@@ -14640,7 +14640,7 @@
         <v>136969516</v>
       </c>
       <c r="B121" t="n">
-        <v>99696</v>
+        <v>99708</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 8191-2026 artfynd.xlsx
+++ b/artfynd/A 8191-2026 artfynd.xlsx
@@ -14640,7 +14640,7 @@
         <v>136969516</v>
       </c>
       <c r="B121" t="n">
-        <v>99708</v>
+        <v>99709</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 8191-2026 artfynd.xlsx
+++ b/artfynd/A 8191-2026 artfynd.xlsx
@@ -14640,7 +14640,7 @@
         <v>136969516</v>
       </c>
       <c r="B121" t="n">
-        <v>99709</v>
+        <v>99712</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 8191-2026 artfynd.xlsx
+++ b/artfynd/A 8191-2026 artfynd.xlsx
@@ -14640,7 +14640,7 @@
         <v>136969516</v>
       </c>
       <c r="B121" t="n">
-        <v>99712</v>
+        <v>99713</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 8191-2026 artfynd.xlsx
+++ b/artfynd/A 8191-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ122"/>
+  <dimension ref="A1:AZ124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2719,48 +2719,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121423769</v>
+        <v>136969508</v>
       </c>
       <c r="B20" t="n">
-        <v>91923</v>
+        <v>92189</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>HACKMORA, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>512493</v>
+        <v>512476</v>
       </c>
       <c r="R20" t="n">
-        <v>6732573</v>
+        <v>6732494</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2784,17 +2784,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På syllstock av gammal husruin</t>
+          <t>resupinat, på sidan, under fastsittande grenar och nedfallna</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2809,49 +2819,49 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121423769</t>
+          <t>https://artportalen.se/Sighting/136969508</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121423752</v>
+        <v>121423769</v>
       </c>
       <c r="B21" t="n">
-        <v>92369</v>
+        <v>91923</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2861,10 +2871,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>512513</v>
+        <v>512493</v>
       </c>
       <c r="R21" t="n">
-        <v>6732688</v>
+        <v>6732573</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2899,6 +2909,11 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På syllstock av gammal husruin</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2922,13 +2937,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121423752</t>
+          <t>https://artportalen.se/Sighting/121423769</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121423753</v>
+        <v>121423752</v>
       </c>
       <c r="B22" t="n">
         <v>92369</v>
@@ -2963,10 +2978,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>512549</v>
+        <v>512513</v>
       </c>
       <c r="R22" t="n">
-        <v>6732434</v>
+        <v>6732688</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3024,16 +3039,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121423753</t>
+          <t>https://artportalen.se/Sighting/121423752</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121423766</v>
+        <v>121423753</v>
       </c>
       <c r="B23" t="n">
-        <v>92143</v>
+        <v>92369</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3041,37 +3056,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1618</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>512622</v>
+        <v>512549</v>
       </c>
       <c r="R23" t="n">
-        <v>6732491</v>
+        <v>6732434</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3110,9 +3122,8 @@
         <v>0</v>
       </c>
       <c r="AE23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF23" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3130,51 +3141,54 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121423766</t>
+          <t>https://artportalen.se/Sighting/121423753</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121423768</v>
+        <v>121423766</v>
       </c>
       <c r="B24" t="n">
-        <v>92632</v>
+        <v>92143</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>1618</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>512478</v>
+        <v>512622</v>
       </c>
       <c r="R24" t="n">
-        <v>6732507</v>
+        <v>6732491</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3213,8 +3227,9 @@
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3232,65 +3247,54 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121423768</t>
+          <t>https://artportalen.se/Sighting/121423766</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121401513</v>
+        <v>136969509</v>
       </c>
       <c r="B25" t="n">
-        <v>91872</v>
+        <v>92531</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hackmora, Dlr</t>
+          <t>HACKMORA, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>512544</v>
+        <v>512477</v>
       </c>
       <c r="R25" t="n">
-        <v>6732488</v>
+        <v>6732497</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3314,22 +3318,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2929, 2950, 2935, 2942, 2939</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3338,7 +3347,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3356,16 +3364,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121401513</t>
+          <t>https://artportalen.se/Sighting/136969509</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121423732</v>
+        <v>121423768</v>
       </c>
       <c r="B26" t="n">
-        <v>91872</v>
+        <v>92632</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3373,21 +3381,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3397,10 +3405,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>512528</v>
+        <v>512478</v>
       </c>
       <c r="R26" t="n">
-        <v>6732678</v>
+        <v>6732507</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3458,13 +3466,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121423732</t>
+          <t>https://artportalen.se/Sighting/121423768</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121423733</v>
+        <v>121401513</v>
       </c>
       <c r="B27" t="n">
         <v>91872</v>
@@ -3492,20 +3500,31 @@
           <t>(Schwein.) Murrill</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>512568</v>
+        <v>512544</v>
       </c>
       <c r="R27" t="n">
-        <v>6732462</v>
+        <v>6732488</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3529,12 +3548,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3543,30 +3572,31 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121423733</t>
+          <t>https://artportalen.se/Sighting/121401513</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121423734</v>
+        <v>121423732</v>
       </c>
       <c r="B28" t="n">
         <v>91872</v>
@@ -3601,10 +3631,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>512545</v>
+        <v>512528</v>
       </c>
       <c r="R28" t="n">
-        <v>6732494</v>
+        <v>6732678</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3662,16 +3692,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121423734</t>
+          <t>https://artportalen.se/Sighting/121423732</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134163553</v>
+        <v>121423733</v>
       </c>
       <c r="B29" t="n">
-        <v>91937</v>
+        <v>91872</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3699,14 +3729,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hackmorkull, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>512491</v>
+        <v>512568</v>
       </c>
       <c r="R29" t="n">
-        <v>6732667</v>
+        <v>6732462</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3733,27 +3763,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>IMG 4829-4833</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3768,49 +3783,49 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134163553</t>
+          <t>https://artportalen.se/Sighting/121423733</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121423773</v>
+        <v>121423734</v>
       </c>
       <c r="B30" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3820,10 +3835,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>512372</v>
+        <v>512545</v>
       </c>
       <c r="R30" t="n">
-        <v>6732682</v>
+        <v>6732494</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3881,51 +3896,51 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121423773</t>
+          <t>https://artportalen.se/Sighting/121423734</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121423774</v>
+        <v>134163553</v>
       </c>
       <c r="B31" t="n">
-        <v>79327</v>
+        <v>91937</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmorkull, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>512377</v>
+        <v>512491</v>
       </c>
       <c r="R31" t="n">
-        <v>6732702</v>
+        <v>6732667</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3952,12 +3967,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>IMG 4829-4833</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3972,24 +4002,24 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121423774</t>
+          <t>https://artportalen.se/Sighting/134163553</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121423775</v>
+        <v>121423773</v>
       </c>
       <c r="B32" t="n">
         <v>79327</v>
@@ -4027,7 +4057,7 @@
         <v>512372</v>
       </c>
       <c r="R32" t="n">
-        <v>6732704</v>
+        <v>6732682</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4085,13 +4115,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121423775</t>
+          <t>https://artportalen.se/Sighting/121423773</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121423785</v>
+        <v>121423774</v>
       </c>
       <c r="B33" t="n">
         <v>79327</v>
@@ -4126,10 +4156,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>512534</v>
+        <v>512377</v>
       </c>
       <c r="R33" t="n">
-        <v>6732503</v>
+        <v>6732702</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4187,13 +4217,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121423785</t>
+          <t>https://artportalen.se/Sighting/121423774</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125816361</v>
+        <v>121423775</v>
       </c>
       <c r="B34" t="n">
         <v>79327</v>
@@ -4224,14 +4254,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>512385</v>
+        <v>512372</v>
       </c>
       <c r="R34" t="n">
-        <v>6732686</v>
+        <v>6732704</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4258,22 +4288,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>22:20</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>22:20</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4288,67 +4308,62 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125816361</t>
+          <t>https://artportalen.se/Sighting/121423775</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121423750</v>
+        <v>121423785</v>
       </c>
       <c r="B35" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>512506</v>
+        <v>512534</v>
       </c>
       <c r="R35" t="n">
-        <v>6732692</v>
+        <v>6732503</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4406,66 +4421,54 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121423750</t>
+          <t>https://artportalen.se/Sighting/121423785</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121425434</v>
+        <v>125816361</v>
       </c>
       <c r="B36" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>512583</v>
+        <v>512385</v>
       </c>
       <c r="R36" t="n">
-        <v>6732462</v>
+        <v>6732686</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4489,17 +4492,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>22:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Gammla hack</t>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>22:20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4514,24 +4522,24 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121425434</t>
+          <t>https://artportalen.se/Sighting/125816361</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125974109</v>
+        <v>121423750</v>
       </c>
       <c r="B37" t="n">
         <v>57950</v>
@@ -4560,27 +4568,24 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>512490</v>
+        <v>512506</v>
       </c>
       <c r="R37" t="n">
-        <v>6732618</v>
+        <v>6732692</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4604,27 +4609,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>20:21</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>20:21</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Granen är nog kring två meter i omkrets.</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4639,27 +4629,27 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125974109</t>
+          <t>https://artportalen.se/Sighting/121423750</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133476452</v>
+        <v>121425434</v>
       </c>
       <c r="B38" t="n">
-        <v>57972</v>
+        <v>57950</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4684,20 +4674,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>512502</v>
+        <v>512583</v>
       </c>
       <c r="R38" t="n">
-        <v>6732589</v>
+        <v>6732462</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4721,22 +4723,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Gammla hack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4751,27 +4748,27 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133476452</t>
+          <t>https://artportalen.se/Sighting/121425434</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136969495</v>
+        <v>125974109</v>
       </c>
       <c r="B39" t="n">
-        <v>58032</v>
+        <v>57950</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4799,18 +4796,22 @@
       <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>HACKMORA, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>512442</v>
+        <v>512490</v>
       </c>
       <c r="R39" t="n">
-        <v>6732415</v>
+        <v>6732618</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4837,27 +4838,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Födosökspår i flera lågor</t>
+          <t>Granen är nog kring två meter i omkrets.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4883,16 +4884,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136969495</t>
+          <t>https://artportalen.se/Sighting/125974109</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136969497</v>
+        <v>133476452</v>
       </c>
       <c r="B40" t="n">
-        <v>58032</v>
+        <v>57972</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4918,20 +4919,16 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>HACKMORA, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>512420</v>
+        <v>512502</v>
       </c>
       <c r="R40" t="n">
-        <v>6732419</v>
+        <v>6732589</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4958,27 +4955,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:23</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Påbörjat bobygge i gran som brutits av ca 3 m upp.</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5004,16 +4996,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136969497</t>
+          <t>https://artportalen.se/Sighting/133476452</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136969507</v>
+        <v>136969495</v>
       </c>
       <c r="B41" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5049,10 +5041,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>512477</v>
+        <v>512442</v>
       </c>
       <c r="R41" t="n">
-        <v>6732502</v>
+        <v>6732415</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5084,7 +5076,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5094,12 +5086,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>I GRANSUMPSKOG i två döda granar.</t>
+          <t>Födosökspår i flera lågor</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5125,16 +5117,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136969507</t>
+          <t>https://artportalen.se/Sighting/136969495</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>136969522</v>
+        <v>136969497</v>
       </c>
       <c r="B42" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5159,11 +5151,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
@@ -5174,10 +5162,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>512488</v>
+        <v>512420</v>
       </c>
       <c r="R42" t="n">
-        <v>6732611</v>
+        <v>6732419</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5209,7 +5197,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5219,12 +5207,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ett bohål är kvar i delen av granen som är kvar efter brottet, minst tre bohål finns i delen som ligger på backen.</t>
+          <t>Påbörjat bobygge i gran som brutits av ca 3 m upp.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5250,33 +5238,33 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136969522</t>
+          <t>https://artportalen.se/Sighting/136969497</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125805740</v>
+        <v>136969507</v>
       </c>
       <c r="B43" t="n">
-        <v>57953</v>
+        <v>58035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5287,25 +5275,21 @@
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>HACKMORA, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>512523</v>
+        <v>512477</v>
       </c>
       <c r="R43" t="n">
-        <v>6732464</v>
+        <v>6732502</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5329,29 +5313,34 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>I GRANSUMPSKOG i två döda granar.</t>
         </is>
       </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="b">
         <v>0</v>
@@ -5370,33 +5359,33 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125805740</t>
+          <t>https://artportalen.se/Sighting/136969507</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125812932</v>
+        <v>136969522</v>
       </c>
       <c r="B44" t="n">
-        <v>57953</v>
+        <v>58035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5404,28 +5393,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>HACKMORA, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>512543</v>
+        <v>512488</v>
       </c>
       <c r="R44" t="n">
-        <v>6732471</v>
+        <v>6732611</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5449,29 +5438,34 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ett bohål är kvar i delen av granen som är kvar efter brottet, minst tre bohål finns i delen som ligger på backen.</t>
         </is>
       </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="b">
         <v>0</v>
@@ -5490,13 +5484,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125812932</t>
+          <t>https://artportalen.se/Sighting/136969522</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125812971</v>
+        <v>125805740</v>
       </c>
       <c r="B45" t="n">
         <v>57953</v>
@@ -5539,10 +5533,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>512539</v>
+        <v>512523</v>
       </c>
       <c r="R45" t="n">
-        <v>6732473</v>
+        <v>6732464</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5574,7 +5568,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5584,7 +5578,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5610,13 +5604,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125812971</t>
+          <t>https://artportalen.se/Sighting/125805740</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125813330</v>
+        <v>125812932</v>
       </c>
       <c r="B46" t="n">
         <v>57953</v>
@@ -5655,14 +5649,14 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>512524</v>
+        <v>512543</v>
       </c>
       <c r="R46" t="n">
-        <v>6732444</v>
+        <v>6732471</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5694,7 +5688,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5704,7 +5698,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5730,13 +5724,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125813330</t>
+          <t>https://artportalen.se/Sighting/125812932</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125814282</v>
+        <v>125812971</v>
       </c>
       <c r="B47" t="n">
         <v>57953</v>
@@ -5765,16 +5759,24 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>512423</v>
+        <v>512539</v>
       </c>
       <c r="R47" t="n">
-        <v>6732722</v>
+        <v>6732473</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5806,7 +5808,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5816,14 +5818,14 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG47" t="b">
         <v>0</v>
@@ -5842,13 +5844,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125814282</t>
+          <t>https://artportalen.se/Sighting/125812971</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125816687</v>
+        <v>125813330</v>
       </c>
       <c r="B48" t="n">
         <v>57953</v>
@@ -5887,14 +5889,14 @@
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>512426</v>
+        <v>512524</v>
       </c>
       <c r="R48" t="n">
-        <v>6732697</v>
+        <v>6732444</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5926,7 +5928,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5936,7 +5938,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5962,13 +5964,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125816687</t>
+          <t>https://artportalen.se/Sighting/125813330</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127784973</v>
+        <v>125814282</v>
       </c>
       <c r="B49" t="n">
         <v>57953</v>
@@ -5997,21 +5999,16 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hackmorkull, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>512564</v>
+        <v>512423</v>
       </c>
       <c r="R49" t="n">
-        <v>6732664</v>
+        <v>6732722</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6038,12 +6035,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6058,27 +6065,27 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127784973</t>
+          <t>https://artportalen.se/Sighting/125814282</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131583623</v>
+        <v>125816687</v>
       </c>
       <c r="B50" t="n">
-        <v>57975</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6114,14 +6121,14 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>512410</v>
+        <v>512426</v>
       </c>
       <c r="R50" t="n">
-        <v>6732734</v>
+        <v>6732697</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6148,34 +6155,29 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>två granar</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG50" t="b">
         <v>0</v>
@@ -6188,22 +6190,22 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131583623</t>
+          <t>https://artportalen.se/Sighting/125816687</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133024788</v>
+        <v>127784973</v>
       </c>
       <c r="B51" t="n">
-        <v>57975</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6229,24 +6231,21 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Hackmorkull, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>512546</v>
+        <v>512564</v>
       </c>
       <c r="R51" t="n">
-        <v>6732422</v>
+        <v>6732664</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6273,27 +6272,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>18:16</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>18:16</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Spår efter födosök på tre granar</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6308,73 +6292,73 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133024788</t>
+          <t>https://artportalen.se/Sighting/127784973</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126029719</v>
+        <v>131583623</v>
       </c>
       <c r="B52" t="n">
-        <v>57945</v>
+        <v>57975</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hackmora, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>512451</v>
+        <v>512410</v>
       </c>
       <c r="R52" t="n">
-        <v>6732710</v>
+        <v>6732734</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6398,27 +6382,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Gråspetten satt i en av alla döda stående granar i närheten av rosentickorna.</t>
+          <t>två granar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6438,44 +6422,44 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126029719</t>
+          <t>https://artportalen.se/Sighting/131583623</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121401275</v>
+        <v>133024788</v>
       </c>
       <c r="B53" t="n">
-        <v>57141</v>
+        <v>57975</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6483,23 +6467,23 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hackmora, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>512405</v>
+        <v>512546</v>
       </c>
       <c r="R53" t="n">
-        <v>6732680</v>
+        <v>6732422</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6523,27 +6507,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Vacker kväll och jag hittade spillningen när jag skulle "ta lunch".</t>
+          <t>Spår efter födosök på tre granar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6563,22 +6547,22 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121401275</t>
+          <t>https://artportalen.se/Sighting/133024788</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125974426</v>
+        <v>126029719</v>
       </c>
       <c r="B54" t="n">
-        <v>57141</v>
+        <v>57945</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6586,21 +6570,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>100110</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6614,17 +6598,17 @@
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>512516</v>
+        <v>512451</v>
       </c>
       <c r="R54" t="n">
-        <v>6732620</v>
+        <v>6732710</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6648,27 +6632,27 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>När jag stod i kanten mot en öppen yta, äng, hörde jag ett "tjäderbrak" i snåren på andra sidan ängen men jag hann bara se en skymt. Kan eventuellt varit samma hona som jag såg trekvart senare.</t>
+          <t>Gråspetten satt i en av alla döda stående granar i närheten av rosentickorna.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6694,13 +6678,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125974426</t>
+          <t>https://artportalen.se/Sighting/126029719</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125976030</v>
+        <v>121401275</v>
       </c>
       <c r="B55" t="n">
         <v>57141</v>
@@ -6728,32 +6712,28 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>512515</v>
+        <v>512405</v>
       </c>
       <c r="R55" t="n">
-        <v>6732684</v>
+        <v>6732680</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6777,27 +6757,27 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Uppflog, såg att det var en hona och kanske var det samma som jag hade sett</t>
+          <t>Vacker kväll och jag hittade spillningen när jag skulle "ta lunch".</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6823,16 +6803,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125976030</t>
+          <t>https://artportalen.se/Sighting/121401275</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131583582</v>
+        <v>125974426</v>
       </c>
       <c r="B56" t="n">
-        <v>57162</v>
+        <v>57141</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6857,25 +6837,25 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>512539</v>
+        <v>512516</v>
       </c>
       <c r="R56" t="n">
-        <v>6732405</v>
+        <v>6732620</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6902,22 +6882,27 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>När jag stod i kanten mot en öppen yta, äng, hörde jag ett "tjäderbrak" i snåren på andra sidan ängen men jag hann bara se en skymt. Kan eventuellt varit samma hona som jag såg trekvart senare.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6937,22 +6922,22 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131583582</t>
+          <t>https://artportalen.se/Sighting/125974426</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127784955</v>
+        <v>125976030</v>
       </c>
       <c r="B57" t="n">
-        <v>4775</v>
+        <v>57141</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,39 +6945,46 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hackmorkull, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>512565</v>
+        <v>512515</v>
       </c>
       <c r="R57" t="n">
-        <v>6732458</v>
+        <v>6732684</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7019,12 +7011,27 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>21:17</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Uppflog, såg att det var en hona och kanske var det samma som jag hade sett</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7039,27 +7046,27 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127784955</t>
+          <t>https://artportalen.se/Sighting/125976030</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121423787</v>
+        <v>131583582</v>
       </c>
       <c r="B58" t="n">
-        <v>5179</v>
+        <v>57162</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7067,34 +7074,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>512531</v>
+        <v>512539</v>
       </c>
       <c r="R58" t="n">
-        <v>6732485</v>
+        <v>6732405</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7121,12 +7136,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7141,27 +7166,27 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121423787</t>
+          <t>https://artportalen.se/Sighting/131583582</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125964674</v>
+        <v>127784955</v>
       </c>
       <c r="B59" t="n">
-        <v>5179</v>
+        <v>4775</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7169,34 +7194,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmorkull, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>512459</v>
+        <v>512565</v>
       </c>
       <c r="R59" t="n">
-        <v>6732421</v>
+        <v>6732458</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7223,22 +7253,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7253,27 +7273,27 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125964674</t>
+          <t>https://artportalen.se/Sighting/127784955</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121423765</v>
+        <v>121423787</v>
       </c>
       <c r="B60" t="n">
-        <v>57132</v>
+        <v>5179</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7281,42 +7301,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102612</v>
+        <v>100526</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>512463</v>
+        <v>512531</v>
       </c>
       <c r="R60" t="n">
-        <v>6732461</v>
+        <v>6732485</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7374,16 +7386,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121423765</t>
+          <t>https://artportalen.se/Sighting/121423787</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121425289</v>
+        <v>125964674</v>
       </c>
       <c r="B61" t="n">
-        <v>57132</v>
+        <v>5179</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7391,38 +7403,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>102612</v>
+        <v>100526</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>512643</v>
+        <v>512459</v>
       </c>
       <c r="R61" t="n">
-        <v>6732557</v>
+        <v>6732421</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7449,24 +7457,29 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>spillning, kändes som Järpe men kände mig osäker eftersom den var lite större än jag tänkt, se bild</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="b">
         <v>0</v>
@@ -7474,24 +7487,24 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121425289</t>
+          <t>https://artportalen.se/Sighting/125964674</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121426321</v>
+        <v>121423765</v>
       </c>
       <c r="B62" t="n">
         <v>57132</v>
@@ -7524,23 +7537,23 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>512598</v>
+        <v>512463</v>
       </c>
       <c r="R62" t="n">
-        <v>6732619</v>
+        <v>6732461</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7567,19 +7580,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7594,27 +7597,27 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121426321</t>
+          <t>https://artportalen.se/Sighting/121423765</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121177799</v>
+        <v>121425289</v>
       </c>
       <c r="B63" t="n">
-        <v>58327</v>
+        <v>57132</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7622,16 +7625,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103015</v>
+        <v>102612</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7639,28 +7642,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hackmorkull, Hackmorkull, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>512531</v>
+        <v>512643</v>
       </c>
       <c r="R63" t="n">
-        <v>6732409</v>
+        <v>6732557</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7684,34 +7683,24 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>10:32</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>10:32</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Jag har hört kungsfåglar på olika platser i området, varje gång jag besökt området.</t>
+          <t>spillning, kändes som Järpe men kände mig osäker eftersom den var lite större än jag tänkt, se bild</t>
         </is>
       </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG63" t="b">
         <v>0</v>
@@ -7719,27 +7708,27 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121177799</t>
+          <t>https://artportalen.se/Sighting/121425289</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121388880</v>
+        <v>121426321</v>
       </c>
       <c r="B64" t="n">
-        <v>58327</v>
+        <v>57132</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7747,16 +7736,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103015</v>
+        <v>102612</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7769,23 +7758,23 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Hackmora, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>512611</v>
+        <v>512598</v>
       </c>
       <c r="R64" t="n">
-        <v>6732496</v>
+        <v>6732619</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7809,22 +7798,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7844,19 +7833,19 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121388880</t>
+          <t>https://artportalen.se/Sighting/121426321</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121388881</v>
+        <v>121177799</v>
       </c>
       <c r="B65" t="n">
         <v>58327</v>
@@ -7884,25 +7873,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hackmora, Dlr</t>
+          <t>Hackmorkull, Hackmorkull, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>512593</v>
+        <v>512531</v>
       </c>
       <c r="R65" t="n">
-        <v>6732493</v>
+        <v>6732409</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7929,27 +7918,27 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Den lät som kungsfåglar låter på hösten.</t>
+          <t>Jag har hört kungsfåglar på olika platser i området, varje gång jag besökt området.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7975,13 +7964,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121388881</t>
+          <t>https://artportalen.se/Sighting/121177799</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125810285</v>
+        <v>121388880</v>
       </c>
       <c r="B66" t="n">
         <v>58327</v>
@@ -8012,21 +8001,25 @@
       <c r="I66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>512560</v>
+        <v>512611</v>
       </c>
       <c r="R66" t="n">
-        <v>6732515</v>
+        <v>6732496</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8050,27 +8043,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>19:18</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Osäker på antal</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8096,13 +8084,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125810285</t>
+          <t>https://artportalen.se/Sighting/121388880</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125973632</v>
+        <v>121388881</v>
       </c>
       <c r="B67" t="n">
         <v>58327</v>
@@ -8135,23 +8123,23 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>512495</v>
+        <v>512593</v>
       </c>
       <c r="R67" t="n">
-        <v>6732470</v>
+        <v>6732493</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8175,27 +8163,27 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Bakom trädskärmen finns ett blötare område med vattenklöver och fläcknycklar.</t>
+          <t>Den lät som kungsfåglar låter på hösten.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8221,62 +8209,58 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125973632</t>
+          <t>https://artportalen.se/Sighting/121388881</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121388879</v>
+        <v>125810285</v>
       </c>
       <c r="B68" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Hackmora, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>512611</v>
+        <v>512560</v>
       </c>
       <c r="R68" t="n">
-        <v>6732496</v>
+        <v>6732515</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8300,27 +8284,27 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Den lät som talltitor låter på hösten</t>
+          <t>Osäker på antal</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8346,38 +8330,38 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121388879</t>
+          <t>https://artportalen.se/Sighting/125810285</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131583625</v>
+        <v>125973632</v>
       </c>
       <c r="B69" t="n">
-        <v>58136</v>
+        <v>58327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8391,14 +8375,14 @@
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>512465</v>
+        <v>512495</v>
       </c>
       <c r="R69" t="n">
-        <v>6732548</v>
+        <v>6732470</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8425,27 +8409,27 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>miljöbild</t>
+          <t>Bakom trädskärmen finns ett blötare område med vattenklöver och fläcknycklar.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8465,60 +8449,68 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131583625</t>
+          <t>https://artportalen.se/Sighting/125973632</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>136969512</v>
+        <v>121388879</v>
       </c>
       <c r="B70" t="n">
-        <v>58191</v>
+        <v>58114</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>HACKMORA, Dlr</t>
+          <t>Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>512485</v>
+        <v>512611</v>
       </c>
       <c r="R70" t="n">
-        <v>6732558</v>
+        <v>6732496</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8542,27 +8534,27 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>ingen bild</t>
+          <t>Den lät som talltitor låter på hösten</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8588,16 +8580,16 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136969512</t>
+          <t>https://artportalen.se/Sighting/121388879</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126586787</v>
+        <v>131583625</v>
       </c>
       <c r="B71" t="n">
-        <v>56522</v>
+        <v>58136</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8605,34 +8597,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>206004</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>512494</v>
+        <v>512465</v>
       </c>
       <c r="R71" t="n">
-        <v>6732599</v>
+        <v>6732548</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8659,22 +8659,27 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>miljöbild</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8700,16 +8705,16 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126586787</t>
+          <t>https://artportalen.se/Sighting/131583625</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125969156</v>
+        <v>136969512</v>
       </c>
       <c r="B72" t="n">
-        <v>58817</v>
+        <v>58194</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8717,47 +8722,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>208249</v>
+        <v>103023</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>HACKMORA, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>512467</v>
+        <v>512485</v>
       </c>
       <c r="R72" t="n">
-        <v>6732466</v>
+        <v>6732558</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8784,27 +8776,27 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>En liten ljusbrun groda med mörkare fläckar och slank kropp.  Jag såg egentligen två på två olika ställen men jag noterade bara koordinaterna på den ena eftersom jag inte hann ta något foto på den. När jag såg en till rapporterade jag den eftersom jag tycker att grodor är viktiga, men jag hann inte ta någon bild på den heller innan den försvann under blåbärsriset.</t>
+          <t>ingen bild</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8813,7 +8805,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8831,33 +8822,33 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125969156</t>
+          <t>https://artportalen.se/Sighting/136969512</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125971105</v>
+        <v>126586787</v>
       </c>
       <c r="B73" t="n">
-        <v>58817</v>
+        <v>56522</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>208249</v>
+        <v>206004</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8865,33 +8856,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>512473</v>
+        <v>512494</v>
       </c>
       <c r="R73" t="n">
-        <v>6732483</v>
+        <v>6732599</v>
       </c>
       <c r="S73" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8915,27 +8893,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>18:40</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>En liten slank ljusbrun groda med mörka fläckar.</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8944,7 +8917,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8956,19 +8928,19 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125971105</t>
+          <t>https://artportalen.se/Sighting/126586787</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126587009</v>
+        <v>125969156</v>
       </c>
       <c r="B74" t="n">
         <v>58817</v>
@@ -8998,27 +8970,31 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>512448</v>
+        <v>512467</v>
       </c>
       <c r="R74" t="n">
-        <v>6732674</v>
+        <v>6732466</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9042,27 +9018,27 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Där det rinner vatten efter stigen strax före Hackmorkull. Det finns säkert fler än två, i avverkningsanmält område.</t>
+          <t>En liten ljusbrun groda med mörkare fläckar och slank kropp.  Jag såg egentligen två på två olika ställen men jag noterade bara koordinaterna på den ena eftersom jag inte hann ta något foto på den. När jag såg en till rapporterade jag den eftersom jag tycker att grodor är viktiga, men jag hann inte ta någon bild på den heller innan den försvann under blåbärsriset.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9083,22 +9059,22 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126587009</t>
+          <t>https://artportalen.se/Sighting/125969156</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125807286</v>
+        <v>125971105</v>
       </c>
       <c r="B75" t="n">
-        <v>99035</v>
+        <v>58817</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9106,49 +9082,50 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219790</v>
+        <v>208249</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>512607</v>
+        <v>512473</v>
       </c>
       <c r="R75" t="n">
-        <v>6732455</v>
+        <v>6732483</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9172,22 +9149,27 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>En liten slank ljusbrun groda med mörka fläckar.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9214,16 +9196,16 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125807286</t>
+          <t>https://artportalen.se/Sighting/125971105</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125809958</v>
+        <v>126587009</v>
       </c>
       <c r="B76" t="n">
-        <v>99035</v>
+        <v>58817</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9231,35 +9213,32 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219790</v>
+        <v>208249</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9267,10 +9246,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>512558</v>
+        <v>512448</v>
       </c>
       <c r="R76" t="n">
-        <v>6732515</v>
+        <v>6732674</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9297,22 +9276,27 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Där det rinner vatten efter stigen strax före Hackmorkull. Det finns säkert fler än två, i avverkningsanmält område.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9333,19 +9317,19 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125809958</t>
+          <t>https://artportalen.se/Sighting/126587009</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125810466</v>
+        <v>125807286</v>
       </c>
       <c r="B77" t="n">
         <v>99035</v>
@@ -9375,7 +9359,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9392,10 +9376,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>512560</v>
+        <v>512607</v>
       </c>
       <c r="R77" t="n">
-        <v>6732515</v>
+        <v>6732455</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9427,7 +9411,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9437,7 +9421,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9464,13 +9448,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125810466</t>
+          <t>https://artportalen.se/Sighting/125807286</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125812392</v>
+        <v>125809958</v>
       </c>
       <c r="B78" t="n">
         <v>99035</v>
@@ -9498,17 +9482,29 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>512543</v>
+        <v>512558</v>
       </c>
       <c r="R78" t="n">
-        <v>6732510</v>
+        <v>6732515</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9540,7 +9536,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9550,7 +9546,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9559,6 +9555,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -9576,13 +9573,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125812392</t>
+          <t>https://artportalen.se/Sighting/125809958</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125813513</v>
+        <v>125810466</v>
       </c>
       <c r="B79" t="n">
         <v>99035</v>
@@ -9610,17 +9607,29 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>512505</v>
+        <v>512560</v>
       </c>
       <c r="R79" t="n">
-        <v>6732477</v>
+        <v>6732515</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9652,7 +9661,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9662,7 +9671,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9671,6 +9680,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -9688,13 +9698,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125813513</t>
+          <t>https://artportalen.se/Sighting/125810466</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125968512</v>
+        <v>125812392</v>
       </c>
       <c r="B80" t="n">
         <v>99035</v>
@@ -9722,32 +9732,20 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>512462</v>
+        <v>512543</v>
       </c>
       <c r="R80" t="n">
-        <v>6732477</v>
+        <v>6732510</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9771,22 +9769,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9795,7 +9793,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9813,13 +9810,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125968512</t>
+          <t>https://artportalen.se/Sighting/125812392</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125969094</v>
+        <v>125813513</v>
       </c>
       <c r="B81" t="n">
         <v>99035</v>
@@ -9854,10 +9851,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>512467</v>
+        <v>512505</v>
       </c>
       <c r="R81" t="n">
-        <v>6732466</v>
+        <v>6732477</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9884,22 +9881,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9925,13 +9922,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125969094</t>
+          <t>https://artportalen.se/Sighting/125813513</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125970965</v>
+        <v>125968512</v>
       </c>
       <c r="B82" t="n">
         <v>99035</v>
@@ -9959,17 +9956,29 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>512473</v>
+        <v>512462</v>
       </c>
       <c r="R82" t="n">
-        <v>6732483</v>
+        <v>6732477</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -10001,7 +10010,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10011,12 +10020,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>18:36</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Inom en radie på fem meter 100st</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10025,6 +10029,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -10042,13 +10047,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125970965</t>
+          <t>https://artportalen.se/Sighting/125968512</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125971419</v>
+        <v>125969094</v>
       </c>
       <c r="B83" t="n">
         <v>99035</v>
@@ -10083,13 +10088,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>512481</v>
+        <v>512467</v>
       </c>
       <c r="R83" t="n">
-        <v>6732503</v>
+        <v>6732466</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10118,7 +10123,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10128,12 +10133,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>18:53</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Kärrviol frånen</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10159,16 +10159,16 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125971419</t>
+          <t>https://artportalen.se/Sighting/125969094</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125810185</v>
+        <v>125970965</v>
       </c>
       <c r="B84" t="n">
-        <v>99022</v>
+        <v>99035</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10176,49 +10176,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>512554</v>
+        <v>512473</v>
       </c>
       <c r="R84" t="n">
-        <v>6732516</v>
+        <v>6732483</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10242,27 +10230,27 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Svårt att säga hur många man ser ju bara dem med blomstänglar.</t>
+          <t>Inom en radie på fem meter 100st</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10271,7 +10259,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -10289,16 +10276,16 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125810185</t>
+          <t>https://artportalen.se/Sighting/125970965</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>134163552</v>
+        <v>125971419</v>
       </c>
       <c r="B85" t="n">
-        <v>111153</v>
+        <v>99035</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10306,37 +10293,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220240</v>
+        <v>219790</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Hackmorkull, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>512423</v>
+        <v>512481</v>
       </c>
       <c r="R85" t="n">
-        <v>6732700</v>
+        <v>6732503</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10360,27 +10347,27 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>vindfälle tall, översållat m linnea</t>
+          <t>Kärrviol frånen</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10406,43 +10393,43 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134163552</t>
+          <t>https://artportalen.se/Sighting/125971419</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121423764</v>
+        <v>125810185</v>
       </c>
       <c r="B86" t="n">
-        <v>99118</v>
+        <v>99022</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10450,16 +10437,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>512489</v>
+        <v>512554</v>
       </c>
       <c r="R86" t="n">
-        <v>6732468</v>
+        <v>6732516</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10486,12 +10476,27 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Svårt att säga hur många man ser ju bara dem med blomstänglar.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10500,76 +10505,69 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121423764</t>
+          <t>https://artportalen.se/Sighting/125810185</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121425292</v>
+        <v>134163552</v>
       </c>
       <c r="B87" t="n">
-        <v>99118</v>
+        <v>111153</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmorkull, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>512561</v>
+        <v>512423</v>
       </c>
       <c r="R87" t="n">
-        <v>6732464</v>
+        <v>6732700</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10596,17 +10594,27 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>varav ca 20 med blomställning</t>
+          <t>vindfälle tall, översållat m linnea</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10615,31 +10623,30 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Beke Regelin, Irina Röjås</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121425292</t>
+          <t>https://artportalen.se/Sighting/134163552</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125811035</v>
+        <v>121423764</v>
       </c>
       <c r="B88" t="n">
         <v>99118</v>
@@ -10669,7 +10676,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10677,23 +10684,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>512578</v>
+        <v>512489</v>
       </c>
       <c r="R88" t="n">
-        <v>6732520</v>
+        <v>6732468</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10720,27 +10720,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>19:37</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>19:37</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Minst 50 Flera med blomstänglar.</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10749,31 +10734,30 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125811035</t>
+          <t>https://artportalen.se/Sighting/121423764</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125967830</v>
+        <v>121425292</v>
       </c>
       <c r="B89" t="n">
         <v>99118</v>
@@ -10803,34 +10787,26 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>512459</v>
+        <v>512561</v>
       </c>
       <c r="R89" t="n">
-        <v>6732486</v>
+        <v>6732464</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10854,22 +10830,17 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>16:40</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>16:40</t>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>varav ca 20 med blomställning</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10885,24 +10856,24 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Beke Regelin, Irina Röjås</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125967830</t>
+          <t>https://artportalen.se/Sighting/121425292</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125969749</v>
+        <v>125811035</v>
       </c>
       <c r="B90" t="n">
         <v>99118</v>
@@ -10930,24 +10901,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>512472</v>
+        <v>512578</v>
       </c>
       <c r="R90" t="n">
-        <v>6732471</v>
+        <v>6732520</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10971,22 +10954,27 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>19:37</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Minst 50 Flera med blomstänglar.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11013,13 +11001,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125969749</t>
+          <t>https://artportalen.se/Sighting/125811035</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125970447</v>
+        <v>125967830</v>
       </c>
       <c r="B91" t="n">
         <v>99118</v>
@@ -11049,7 +11037,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -11059,7 +11047,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -11070,10 +11058,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>512475</v>
+        <v>512459</v>
       </c>
       <c r="R91" t="n">
-        <v>6732479</v>
+        <v>6732486</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -11105,7 +11093,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11115,12 +11103,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>18:16</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Däremot fanns inga blomstänglar just här.</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11147,13 +11130,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125970447</t>
+          <t>https://artportalen.se/Sighting/125967830</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125972943</v>
+        <v>125969749</v>
       </c>
       <c r="B92" t="n">
         <v>99118</v>
@@ -11181,16 +11164,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
@@ -11200,10 +11175,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>512495</v>
+        <v>512472</v>
       </c>
       <c r="R92" t="n">
-        <v>6732470</v>
+        <v>6732471</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -11235,7 +11210,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11245,12 +11220,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>19:47</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>uppskattat antal.</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11277,58 +11247,70 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125972943</t>
+          <t>https://artportalen.se/Sighting/125969749</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127085273</v>
+        <v>125970447</v>
       </c>
       <c r="B93" t="n">
-        <v>102240</v>
+        <v>99118</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221235</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Hackmorkull, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>512526</v>
+        <v>512475</v>
       </c>
       <c r="R93" t="n">
-        <v>6732574</v>
+        <v>6732479</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11352,12 +11334,27 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Däremot fanns inga blomstänglar just här.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11373,54 +11370,54 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127085273</t>
+          <t>https://artportalen.se/Sighting/125970447</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125810697</v>
+        <v>125972943</v>
       </c>
       <c r="B94" t="n">
-        <v>106229</v>
+        <v>99118</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11433,17 +11430,17 @@
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>512560</v>
+        <v>512495</v>
       </c>
       <c r="R94" t="n">
-        <v>6732515</v>
+        <v>6732470</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11467,27 +11464,27 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Så liten, så skör och så vacker!</t>
+          <t>uppskattat antal.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11514,63 +11511,55 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125810697</t>
+          <t>https://artportalen.se/Sighting/125972943</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125811364</v>
+        <v>127085273</v>
       </c>
       <c r="B95" t="n">
-        <v>106229</v>
+        <v>102240</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221725</v>
+        <v>221235</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Hackmorkull, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>512579</v>
+        <v>512526</v>
       </c>
       <c r="R95" t="n">
-        <v>6732525</v>
+        <v>6732574</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11597,27 +11586,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>19:48</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>19:48</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Uppskattat antal, blommande, knopp och plantor utan.</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11633,24 +11607,24 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125811364</t>
+          <t>https://artportalen.se/Sighting/127085273</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125812445</v>
+        <v>125810697</v>
       </c>
       <c r="B96" t="n">
         <v>106229</v>
@@ -11678,17 +11652,29 @@
           <t>(L.) A. Gray</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>512543</v>
+        <v>512560</v>
       </c>
       <c r="R96" t="n">
-        <v>6732510</v>
+        <v>6732515</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11720,7 +11706,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11730,7 +11716,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Så liten, så skör och så vacker!</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11739,6 +11730,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -11756,16 +11748,16 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125812445</t>
+          <t>https://artportalen.se/Sighting/125810697</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121179502</v>
+        <v>125811364</v>
       </c>
       <c r="B97" t="n">
-        <v>97983</v>
+        <v>106229</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11773,31 +11765,31 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -11805,17 +11797,17 @@
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Hackmorkull, Hackmorkull, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>512532</v>
+        <v>512579</v>
       </c>
       <c r="R97" t="n">
-        <v>6732598</v>
+        <v>6732525</v>
       </c>
       <c r="S97" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11839,27 +11831,27 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>10x3 m, uppskattat område</t>
+          <t>Uppskattat antal, blommande, knopp och plantor utan.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11886,16 +11878,16 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121179502</t>
+          <t>https://artportalen.se/Sighting/125811364</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121399884</v>
+        <v>125812445</v>
       </c>
       <c r="B98" t="n">
-        <v>97983</v>
+        <v>106229</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11903,41 +11895,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Hackmora, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>512569</v>
+        <v>512543</v>
       </c>
       <c r="R98" t="n">
-        <v>6732458</v>
+        <v>6732510</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11961,22 +11949,22 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11985,7 +11973,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -12003,13 +11990,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121399884</t>
+          <t>https://artportalen.se/Sighting/125812445</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121425291</v>
+        <v>121179502</v>
       </c>
       <c r="B99" t="n">
         <v>97983</v>
@@ -12037,20 +12024,32 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmorkull, Hackmorkull, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>512552</v>
+        <v>512532</v>
       </c>
       <c r="R99" t="n">
-        <v>6732510</v>
+        <v>6732598</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12074,12 +12073,27 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>10x3 m, uppskattat område</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12088,30 +12102,31 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121425291</t>
+          <t>https://artportalen.se/Sighting/121179502</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125971792</v>
+        <v>121399884</v>
       </c>
       <c r="B100" t="n">
         <v>97983</v>
@@ -12139,32 +12154,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>512451</v>
+        <v>512569</v>
       </c>
       <c r="R100" t="n">
-        <v>6732445</v>
+        <v>6732458</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12188,27 +12195,22 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>19:17</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Minst sex mindre grupper på en mindre yta.</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12235,13 +12237,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125971792</t>
+          <t>https://artportalen.se/Sighting/121399884</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126586715</v>
+        <v>121425291</v>
       </c>
       <c r="B101" t="n">
         <v>97983</v>
@@ -12269,29 +12271,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>512493</v>
+        <v>512552</v>
       </c>
       <c r="R101" t="n">
-        <v>6732582</v>
+        <v>6732510</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12318,27 +12308,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>15:42</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Betespräglad fäbodskog, olika ormbunkar, ormbär, ekorrbär, asp, rönn, björk, gran</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12347,31 +12322,30 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126586715</t>
+          <t>https://artportalen.se/Sighting/121425291</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127085227</v>
+        <v>125971792</v>
       </c>
       <c r="B102" t="n">
         <v>97983</v>
@@ -12399,20 +12373,32 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Hackmorkull, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>512526</v>
+        <v>512451</v>
       </c>
       <c r="R102" t="n">
-        <v>6732591</v>
+        <v>6732445</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12436,12 +12422,27 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Minst sex mindre grupper på en mindre yta.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12450,33 +12451,34 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127085227</t>
+          <t>https://artportalen.se/Sighting/125971792</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125809649</v>
+        <v>126586715</v>
       </c>
       <c r="B103" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12484,31 +12486,31 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -12516,14 +12518,14 @@
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>512552</v>
+        <v>512493</v>
       </c>
       <c r="R103" t="n">
-        <v>6732505</v>
+        <v>6732582</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12550,27 +12552,27 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Några i blom</t>
+          <t>Betespräglad fäbodskog, olika ormbunkar, ormbär, ekorrbär, asp, rönn, björk, gran</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12591,22 +12593,22 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125809649</t>
+          <t>https://artportalen.se/Sighting/126586715</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125809802</v>
+        <v>127085227</v>
       </c>
       <c r="B104" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12614,46 +12616,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Hackmorkull, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>512547</v>
+        <v>512526</v>
       </c>
       <c r="R104" t="n">
-        <v>6732517</v>
+        <v>6732591</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12680,22 +12670,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>19:02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>19:02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12704,31 +12684,30 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125809802</t>
+          <t>https://artportalen.se/Sighting/127085227</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125810907</v>
+        <v>125809649</v>
       </c>
       <c r="B105" t="n">
         <v>99140</v>
@@ -12758,7 +12737,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -12775,10 +12754,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>512578</v>
+        <v>512552</v>
       </c>
       <c r="R105" t="n">
-        <v>6732520</v>
+        <v>6732505</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12810,7 +12789,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12820,12 +12799,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Några i blom och några utan blommor</t>
+          <t>Några i blom</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12852,13 +12831,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125810907</t>
+          <t>https://artportalen.se/Sighting/125809649</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125812085</v>
+        <v>125809802</v>
       </c>
       <c r="B106" t="n">
         <v>99140</v>
@@ -12888,7 +12867,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -12896,23 +12875,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>512564</v>
+        <v>512547</v>
       </c>
       <c r="R106" t="n">
-        <v>6732513</v>
+        <v>6732517</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12944,7 +12919,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12954,12 +12929,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>20:11</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Så små och så sköra. De kan aldrig överleva en avverkning och inte marken de växter i heller. Det finns en hel del blad men alla plantor blommar inte.</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12986,13 +12956,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125812085</t>
+          <t>https://artportalen.se/Sighting/125809802</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125968150</v>
+        <v>125810907</v>
       </c>
       <c r="B107" t="n">
         <v>99140</v>
@@ -13022,7 +12992,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -13035,17 +13005,17 @@
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>512450</v>
+        <v>512578</v>
       </c>
       <c r="R107" t="n">
-        <v>6732474</v>
+        <v>6732520</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13069,27 +13039,27 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Några blommade. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
+          <t>Några i blom och några utan blommor</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13116,13 +13086,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125968150</t>
+          <t>https://artportalen.se/Sighting/125810907</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125969726</v>
+        <v>125812085</v>
       </c>
       <c r="B108" t="n">
         <v>99140</v>
@@ -13152,7 +13122,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -13173,13 +13143,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>512469</v>
+        <v>512564</v>
       </c>
       <c r="R108" t="n">
-        <v>6732470</v>
+        <v>6732513</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13203,27 +13173,27 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
+          <t>Så små och så sköra. De kan aldrig överleva en avverkning och inte marken de växter i heller. Det finns en hel del blad men alla plantor blommar inte.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13250,13 +13220,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125969726</t>
+          <t>https://artportalen.se/Sighting/125812085</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125970625</v>
+        <v>125968150</v>
       </c>
       <c r="B109" t="n">
         <v>99140</v>
@@ -13286,7 +13256,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -13294,11 +13264,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
@@ -13307,10 +13273,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>512475</v>
+        <v>512450</v>
       </c>
       <c r="R109" t="n">
-        <v>6732479</v>
+        <v>6732474</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -13342,7 +13308,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13352,12 +13318,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Jag hade redan registrerat 100 när jag såg att de var flera. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
+          <t>Några blommade. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13384,13 +13350,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125970625</t>
+          <t>https://artportalen.se/Sighting/125968150</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125971336</v>
+        <v>125969726</v>
       </c>
       <c r="B110" t="n">
         <v>99140</v>
@@ -13420,7 +13386,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -13428,7 +13394,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
@@ -13437,10 +13407,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>512484</v>
+        <v>512469</v>
       </c>
       <c r="R110" t="n">
-        <v>6732491</v>
+        <v>6732470</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -13472,7 +13442,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13482,7 +13452,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
@@ -13514,13 +13484,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125971336</t>
+          <t>https://artportalen.se/Sighting/125969726</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125971458</v>
+        <v>125970625</v>
       </c>
       <c r="B111" t="n">
         <v>99140</v>
@@ -13548,9 +13518,21 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
@@ -13559,10 +13541,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>512481</v>
+        <v>512475</v>
       </c>
       <c r="R111" t="n">
-        <v>6732503</v>
+        <v>6732479</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -13594,7 +13576,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13604,12 +13586,12 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
+          <t>Jag hade redan registrerat 100 när jag såg att de var flera. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13636,13 +13618,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125971458</t>
+          <t>https://artportalen.se/Sighting/125970625</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125972442</v>
+        <v>125971336</v>
       </c>
       <c r="B112" t="n">
         <v>99140</v>
@@ -13672,7 +13654,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -13680,11 +13662,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
@@ -13693,10 +13671,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>512481</v>
+        <v>512484</v>
       </c>
       <c r="R112" t="n">
-        <v>6732473</v>
+        <v>6732491</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -13728,7 +13706,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13738,7 +13716,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
@@ -13770,16 +13748,16 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125972442</t>
+          <t>https://artportalen.se/Sighting/125971336</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121423789</v>
+        <v>125971458</v>
       </c>
       <c r="B113" t="n">
-        <v>101326</v>
+        <v>99140</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13787,37 +13765,41 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>512635</v>
+        <v>512481</v>
       </c>
       <c r="R113" t="n">
-        <v>6732571</v>
+        <v>6732503</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13841,12 +13823,27 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13855,33 +13852,34 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121423789</t>
+          <t>https://artportalen.se/Sighting/125971458</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121423790</v>
+        <v>125972442</v>
       </c>
       <c r="B114" t="n">
-        <v>101326</v>
+        <v>99140</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13889,37 +13887,53 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>512628</v>
+        <v>512481</v>
       </c>
       <c r="R114" t="n">
-        <v>6732540</v>
+        <v>6732473</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13943,12 +13957,27 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13957,30 +13986,31 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121423790</t>
+          <t>https://artportalen.se/Sighting/125972442</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121423791</v>
+        <v>121423789</v>
       </c>
       <c r="B115" t="n">
         <v>101326</v>
@@ -14015,10 +14045,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>512638</v>
+        <v>512635</v>
       </c>
       <c r="R115" t="n">
-        <v>6732516</v>
+        <v>6732571</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14076,13 +14106,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121423791</t>
+          <t>https://artportalen.se/Sighting/121423789</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121423792</v>
+        <v>121423790</v>
       </c>
       <c r="B116" t="n">
         <v>101326</v>
@@ -14120,7 +14150,7 @@
         <v>512628</v>
       </c>
       <c r="R116" t="n">
-        <v>6732517</v>
+        <v>6732540</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14178,13 +14208,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121423792</t>
+          <t>https://artportalen.se/Sighting/121423790</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121425050</v>
+        <v>121423791</v>
       </c>
       <c r="B117" t="n">
         <v>101326</v>
@@ -14213,23 +14243,19 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>512609</v>
+        <v>512638</v>
       </c>
       <c r="R117" t="n">
-        <v>6732541</v>
+        <v>6732516</v>
       </c>
       <c r="S117" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14256,52 +14282,41 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121425050</t>
+          <t>https://artportalen.se/Sighting/121423791</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121425051</v>
+        <v>121423792</v>
       </c>
       <c r="B118" t="n">
         <v>101326</v>
@@ -14330,23 +14345,19 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>512639</v>
+        <v>512628</v>
       </c>
       <c r="R118" t="n">
-        <v>6732526</v>
+        <v>6732517</v>
       </c>
       <c r="S118" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -14373,52 +14384,41 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121425051</t>
+          <t>https://artportalen.se/Sighting/121423792</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121425052</v>
+        <v>121425050</v>
       </c>
       <c r="B119" t="n">
         <v>101326</v>
@@ -14457,10 +14457,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>512626</v>
+        <v>512609</v>
       </c>
       <c r="R119" t="n">
-        <v>6732514</v>
+        <v>6732541</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -14492,7 +14492,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -14502,7 +14502,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14529,13 +14529,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121425052</t>
+          <t>https://artportalen.se/Sighting/121425050</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127784976</v>
+        <v>121425051</v>
       </c>
       <c r="B120" t="n">
         <v>101326</v>
@@ -14564,19 +14564,23 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Hackmorkull, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>512517</v>
+        <v>512639</v>
       </c>
       <c r="R120" t="n">
-        <v>6732569</v>
+        <v>6732526</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14600,12 +14604,22 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14614,33 +14628,34 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127784976</t>
+          <t>https://artportalen.se/Sighting/121425051</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>136969516</v>
+        <v>121425052</v>
       </c>
       <c r="B121" t="n">
-        <v>99713</v>
+        <v>101326</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14648,37 +14663,41 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>222812</v>
+        <v>222498</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>HACKMORA, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>512496</v>
+        <v>512626</v>
       </c>
       <c r="R121" t="n">
-        <v>6732586</v>
+        <v>6732514</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14702,27 +14721,22 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>3100 bären</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14731,6 +14745,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -14742,22 +14757,22 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136969516</t>
+          <t>https://artportalen.se/Sighting/121425052</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121426318</v>
+        <v>127784976</v>
       </c>
       <c r="B122" t="n">
-        <v>97985</v>
+        <v>101326</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14765,37 +14780,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>224363</v>
+        <v>222498</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Hackmorkull, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>512584</v>
+        <v>512517</v>
       </c>
       <c r="R122" t="n">
-        <v>6732486</v>
+        <v>6732569</v>
       </c>
       <c r="S122" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14819,22 +14834,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>09:48</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>09:48</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14843,23 +14848,252 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784976</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>136969516</v>
+      </c>
+      <c r="B123" t="n">
+        <v>99716</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>HACKMORA, Dlr</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>512496</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6732586</v>
+      </c>
+      <c r="S123" t="n">
+        <v>5</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>3100 bären</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136969516</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>121426318</v>
+      </c>
+      <c r="B124" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>512584</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6732486</v>
+      </c>
+      <c r="S124" t="n">
+        <v>15</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/121426318</t>
         </is>
@@ -14988,6 +15222,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
